--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -581,6 +581,11 @@
           <t>실행여부</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>분析대상</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -601,6 +606,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -621,6 +631,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="n">
@@ -641,6 +656,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -661,6 +681,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2" t="n">
@@ -681,6 +706,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -699,6 +729,11 @@
       <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>당기</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -13,6 +13,7 @@
     <sheet name="거액전표" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="상세검색" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="라운드넘버" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="특수관계자" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -734,6 +735,31 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>특수관계자분析</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>특수관계자 거래처 거래 추출 → 특수관계자 시트 참조</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>전체</t>
         </is>
       </c>
     </row>
@@ -1326,4 +1352,51 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,25 +15,35 @@
     <sheet name="특수관계자" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -46,17 +55,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5496"/>
+        <fgColor rgb="FF2F5496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,23 +79,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -97,9 +107,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -463,7 +479,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -495,10 +511,10 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>㈜그래피</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+          <t>㈜세중</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -506,10 +522,8 @@
           <t>StartDate</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+      <c r="B3" s="4" t="n">
+        <v>46023</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
@@ -523,12 +537,10 @@
           <t>EndDate</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="B4" s="5" t="n">
+        <v>46387</v>
+      </c>
+      <c r="C4" s="2" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -537,9 +549,9 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
+        <v>2026</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -552,8 +564,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -590,16 +602,16 @@
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>공휴일전표</t>
+          <t>거래처 전기/당기 비교</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>토·일·공휴일 입력 전표 추출 (파라미터 불필요)</t>
+          <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -615,16 +627,16 @@
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>중복전표</t>
+          <t>벤포드 분析</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>날짜·계정·금액·거래처 중복 전표 추출 (파라미터 불필요)</t>
+          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분析 시트 참조</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -634,27 +646,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>당기</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>벤포드분析</t>
+          <t>데이터 개요</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분析 시트 참조</t>
+          <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -669,17 +681,17 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>거액전표</t>
+          <t>계정명 리스트</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>상위 N% 거액 전표 추출 → 거액전표 시트 참조</t>
+          <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,17 +706,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>상세검색</t>
+          <t>사원별 집계</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>계정/거래처/적요 복합 조건 검색 → 상세검색 시트 참조</t>
+          <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -715,21 +727,21 @@
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>라운드넘버</t>
+          <t>일자차이 분析</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
+          <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분析 시트 참조</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -740,24 +752,299 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>상대계정 분析</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>특정 계정의 상대계정 분析 → 상대계정분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>키워드 검색</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>적요 키워드 검색 → 키워드검색 시트 참조</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>라운드넘버 분析</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>11</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>특수관계자분析</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>특수관계자 분析</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>특수관계자 거래처 거래 추출 → 특수관계자 시트 참조</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>자산 vs 부채 교차</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>자산/부채 동시 발생 거래처 分析</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>매출 vs 비용 교차</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>매출/비용 동시 발생 거래처 分析</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>심층분析 (계정별 Top)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>계정별 거래처 Top N 추출 → 심층분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AI 계정별 분析</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>데이터·헤더 확인</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>컬럼 인식 현황 점검 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>거래처 분析</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>특정 거래처 복합조건 상세 分析 → 거래처분析 시트 참조</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>벤포드 이탈 상세 추출</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>벤포드 이탈 전표 상세 추출 → 벤포드이탈 시트 참조</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>월별 전계정 分析</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>전 계정 월별 차변/대변 집계 (파라미터 불필요)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
@@ -775,7 +1062,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -821,7 +1108,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -839,7 +1126,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -857,7 +1144,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -875,7 +1162,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -911,7 +1198,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1034,15 +1321,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1104,7 +1390,7 @@
           <t>GRAPHY SMA</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>대변만</t>
@@ -1134,7 +1420,7 @@
           <t>GRAPHY SMA</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>차변만</t>
@@ -1159,8 +1445,8 @@
           <t>기계장치</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>차변만</t>
@@ -1187,8 +1473,8 @@
           <t>보통예금</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>양방향</t>
@@ -1210,8 +1496,8 @@
           <t>특정적요_검색</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>가지급</t>
@@ -1242,7 +1528,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1322,7 +1608,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1361,13 +1647,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
+      <c r="A1" t="n">
+        <v>11</v>
       </c>
       <c r="B1" t="inlineStr">
         <is>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -8,11 +8,9 @@
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="분析목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="벤포드분析" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="거액전표" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="상세검색" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="라운드넘버" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="특수관계자" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="벤포드 분析" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="라운드넘버 분析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="특수관계자 분析" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1202,9 +1200,9 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -1220,7 +1218,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>기준백분위(%)</t>
+          <t>최소금액</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1246,7 +1244,7 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>99</v>
+        <v>100000</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -1255,7 +1253,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>상위 1% 이상</t>
+          <t>10만원 이상 라운드 수 탐지</t>
         </is>
       </c>
     </row>
@@ -1271,23 +1269,19 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>99</v>
+        <v>100000</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>상위 1% 이상</t>
-        </is>
-      </c>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>외상매출금</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1296,7 +1290,7 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>95</v>
+        <v>500000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -1305,7 +1299,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>특정 계정 기준 조정 시 활성화</t>
+          <t>보통예금만 50만원 기준 (선택)</t>
         </is>
       </c>
     </row>
@@ -1320,332 +1314,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>작업명</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>적요</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>금액유형</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>최소금액</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>최대금액</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>특수관계자_매출</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>외상매출금</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>GRAPHY SMA</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>대변만</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>특수관계자_매입</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>외상매입금</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>GRAPHY SMA</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>차변만</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>유형자산취득</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>기계장치</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>차변만</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>고액_현금성거래</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>양방향</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>특정적요_검색</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>가지급</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>양방향</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>최소금액</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>10만원 이상 라운드 수 탐지</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>보통예금만 50만원 기준 (선택)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <sheetData>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -7,10 +7,10 @@
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="분析목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="벤포드 분析" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="라운드넘버 분析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="특수관계자 분析" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="벤포드 분석" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="라운드넘버 분석" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="특수관계자 분석" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -574,12 +574,12 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>분析번호</t>
+          <t>분석번호</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>분析명</t>
+          <t>분석명</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>분析대상</t>
+          <t>분석대상</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>벤포드 분析</t>
+          <t>벤포드 분석</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분析 시트 참조</t>
+          <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분석 시트 참조</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>일자차이 분析</t>
+          <t>일자차이 분석</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분析 시트 참조</t>
+          <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분석 시트 참조</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>상대계정 분析</t>
+          <t>상대계정 분석</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>특정 계정의 상대계정 분析 → 상대계정분析 시트 참조</t>
+          <t>특정 계정의 상대계정 분석 → 상대계정분석 시트 참조</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>라운드넘버 분析</t>
+          <t>라운드넘버 분석</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>특수관계자 분析</t>
+          <t>특수관계자 분석</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>자산/부채 동시 발생 거래처 分析</t>
+          <t>자산/부채 동시 발생 거래처 분석</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>매출/비용 동시 발생 거래처 分析</t>
+          <t>매출/비용 동시 발생 거래처 분석</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>심층분析 (계정별 Top)</t>
+          <t>심층분석 (계정별 Top)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>계정별 거래처 Top N 추출 → 심층분析 시트 참조</t>
+          <t>계정별 거래처 Top N 추출 → 심층분석 시트 참조</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AI 계정별 분析</t>
+          <t>AI 계정별 분석</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분析 시트 참조</t>
+          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>거래처 분析</t>
+          <t>거래처 분석</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>특정 거래처 복합조건 상세 分析 → 거래처분析 시트 참조</t>
+          <t>특정 거래처 복합조건 상세 분석 → 거래처분석 시트 참조</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>월별 전계정 分析</t>
+          <t>월별 전계정 분석</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -1,31 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\journal_analyzer\sejoong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C206AB78-CD59-490F-ADAD-8C91C290072F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB5788A-30F6-462E-87B6-86869ED1C49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" r:id="rId2"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="6" r:id="rId3"/>
-    <sheet name="벤포드 분석" sheetId="3" r:id="rId4"/>
-    <sheet name="라운드넘버 분석" sheetId="4" r:id="rId5"/>
-    <sheet name="특수관계자 분석" sheetId="5" r:id="rId6"/>
+    <sheet name="심층분석 (계정별 Top) " sheetId="9" r:id="rId3"/>
+    <sheet name="총계정원장" sheetId="10" r:id="rId4"/>
+    <sheet name="거래처 전기_당기 비교" sheetId="6" r:id="rId5"/>
+    <sheet name="상대계정 분석" sheetId="7" r:id="rId6"/>
+    <sheet name="벤포드 분석" sheetId="3" r:id="rId7"/>
+    <sheet name="라운드넘버 분석" sheetId="4" r:id="rId8"/>
+    <sheet name="매출 vs 비용 교차" sheetId="8" r:id="rId9"/>
+    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="11" r:id="rId10"/>
+    <sheet name="1" sheetId="12" r:id="rId11"/>
+    <sheet name="특수관계자 분석" sheetId="5" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="171">
   <si>
     <t>분석번호</t>
   </si>
@@ -192,15 +211,9 @@
     <t>금액열</t>
   </si>
   <si>
-    <t>외상매출금</t>
-  </si>
-  <si>
     <t>차변</t>
   </si>
   <si>
-    <t>외상매입금</t>
-  </si>
-  <si>
     <t>대변</t>
   </si>
   <si>
@@ -210,22 +223,9 @@
     <t>(전체)</t>
   </si>
   <si>
-    <t>전체 계정 — 데이터 많을 경우 느릴 수 있음</t>
-  </si>
-  <si>
     <t>최소금액</t>
   </si>
   <si>
-    <t>10만원 이상 라운드 수 탐지</t>
-  </si>
-  <si>
-    <t>보통예금만 50만원 기준 (선택)</t>
-  </si>
-  <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Y</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -234,39 +234,367 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>4,5,6,16,19</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있었도 분석실행 안 됨</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>분 분석목록시트에 실행여부가 Y이고 과련분서시트가 없으면 기본분석값으로 실행</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미수금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>차변</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>미수대매금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>용역매출</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>대변</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>거래처 전기_당기 비교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분 분석목록시트에 실행여부가 Y이고 관련분서시트가 없으면 기본분석값으로 실행</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미수대매금(국제항공권판매)</t>
+  </si>
+  <si>
+    <t>항공권판매(국제)</t>
+  </si>
+  <si>
+    <t>외상매출금(PLM)</t>
+  </si>
+  <si>
+    <t>미수금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>미수금(기 타)</t>
+  </si>
+  <si>
+    <t>상품매출액(PLM)</t>
+  </si>
+  <si>
+    <t>용역매출액(S&amp;C)</t>
+  </si>
+  <si>
+    <t>미지급금(일반)</t>
+  </si>
+  <si>
+    <t>외상매출금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>매출액(기타항공권판매수입)</t>
+  </si>
+  <si>
+    <t>매출액(해외여행알선수입)</t>
+  </si>
+  <si>
+    <t>예수금(국제항공권환불)</t>
+  </si>
+  <si>
+    <t>미수금(국제항공취급수수료)</t>
+  </si>
+  <si>
+    <t>선급금(입체금-국내관광알선)</t>
+  </si>
+  <si>
+    <t>선수금(국제항공권)</t>
+  </si>
+  <si>
+    <t>매출액(국제항공취급수수료)</t>
+  </si>
+  <si>
+    <t>계정과목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품매출액(S&amp;C)</t>
+  </si>
+  <si>
+    <t>비용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지급수수료(S&amp;C)</t>
+  </si>
+  <si>
+    <t>지급수수료(PLM)</t>
+  </si>
+  <si>
+    <t>접대비</t>
+  </si>
+  <si>
+    <t>㈜세중샤론손해보험</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표이사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜세중엔지니어링</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재)우리옛돌문화재단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜세중인터내셔널</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜세성항운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천신일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천세전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천호전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천미전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔액증감분석 (계정별 거래처별)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 계정별 거래처별로 기초잔액 증가 감소 기말 잔액 추출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계저영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금(보험가입대급금)</t>
+  </si>
+  <si>
+    <t>선급금(에스앤씨)</t>
+  </si>
+  <si>
+    <t>선급금(여권및비자대)</t>
+  </si>
+  <si>
+    <t>선급금(일반)</t>
+  </si>
+  <si>
+    <t>선급금(입체금-해외여행알선)</t>
+  </si>
+  <si>
+    <t>미수금(국내관광알선)</t>
+  </si>
+  <si>
+    <t>미수금(국내항공권-정산)</t>
+  </si>
+  <si>
+    <t>미수금(국내항공취급수수료)</t>
+  </si>
+  <si>
+    <t>미수금(국제항공권-정산)</t>
+  </si>
+  <si>
+    <t>미수금(기타)</t>
+  </si>
+  <si>
+    <t>미수금(에스앤씨)</t>
+  </si>
+  <si>
+    <t>미수금(여권비자취급수수료)</t>
+  </si>
+  <si>
+    <t>미수금(정보기술)</t>
+  </si>
+  <si>
+    <t>미수금(카드판매)</t>
+  </si>
+  <si>
+    <t>미수금(해외여행환불)</t>
+  </si>
+  <si>
+    <t>미수금(호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>미수대매금(국내항공권판매)</t>
+  </si>
+  <si>
+    <t>미수대매금(국제항공권판매 ADM)</t>
+  </si>
+  <si>
+    <t>단기대여금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기대여금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>총계정원장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기/당기/전당기 기간의 게정별 월별합계 차/대/전체로 추출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가수금</t>
+  </si>
+  <si>
+    <t>자산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미수금환불(국제항공)</t>
+  </si>
+  <si>
+    <t>정기예금</t>
+  </si>
+  <si>
+    <t>수탁금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>투자매도가능증권</t>
+  </si>
+  <si>
+    <t>상품(PLM)</t>
+  </si>
+  <si>
+    <t>상품(S&amp;C)</t>
+  </si>
+  <si>
+    <t>수탁금(호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>선급금(입체금-호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>선급금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>정기성예금</t>
+  </si>
+  <si>
+    <t>장기대여금</t>
+  </si>
+  <si>
+    <t>미수수익</t>
+  </si>
+  <si>
+    <t>외화예금</t>
+  </si>
+  <si>
+    <t>미지급금(국제항공권-정산)</t>
+  </si>
+  <si>
+    <t>선수금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>외상매입금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>미지급금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>외상매입금(PLM)</t>
+  </si>
+  <si>
+    <t>미지급금(호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>미지급금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>예수금(결산)</t>
+  </si>
+  <si>
+    <t>미지급금(회사카드사용분-단체)</t>
+  </si>
+  <si>
+    <t>예수금(갑근세)</t>
+  </si>
+  <si>
+    <t>부채</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공권판매(국제항공취급수수료)</t>
+  </si>
+  <si>
+    <t>매출액(해외호텔알선수입)</t>
+  </si>
+  <si>
+    <t>용역매출액(PLM)</t>
+  </si>
+  <si>
+    <t>매출액(국내관광알선수입)</t>
+  </si>
+  <si>
+    <t>매출액(국제항공권판매수입)</t>
+  </si>
+  <si>
+    <t>매출액(여권비자취급수수료)</t>
+  </si>
+  <si>
+    <t>매출액(국내호텔콘도알선수입)</t>
+  </si>
+  <si>
+    <t>매출액(기타)</t>
+  </si>
+  <si>
+    <t>매출액(국내항공취급수수료)</t>
+  </si>
+  <si>
+    <t>매출액(국내항공권판매수입)</t>
+  </si>
+  <si>
+    <t>매출액</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행조회서 완전성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이자비용, 장단기차입금, 전환사채, RCPS등의 거래처와 은행조회서 발송내역 비교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,5,6,16,19,22</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -274,7 +602,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,6 +626,13 @@
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -321,7 +659,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -344,11 +682,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -374,8 +729,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="쉼표 [0] 2" xfId="2" xr:uid="{15187B96-CFD2-4E93-A69C-206B9D1FF7B9}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -739,14 +1114,348 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D312E48-8E6E-493E-8A48-BE945225BF96}">
+  <dimension ref="A1:B27"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="30.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA246E49-9EB8-4E4E-9005-B617F351DDBE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B12" s="8"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="27.83203125" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="3" max="3" width="72.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -773,7 +1482,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -830,7 +1539,7 @@
         <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -881,7 +1590,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -966,7 +1675,7 @@
         <v>31</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -983,7 +1692,7 @@
         <v>33</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -1017,7 +1726,7 @@
         <v>37</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -1068,28 +1777,79 @@
         <v>43</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="8">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="8">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="8">
+        <v>22</v>
+      </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>69</v>
+        <v>168</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>70</v>
+        <v>61</v>
+      </c>
+      <c r="C24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1099,11 +1859,508 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86F7D49D-FC4F-438B-AE4B-40B32B4CF7EC}">
-  <dimension ref="A1:D4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3654F5BB-5023-4650-B10F-E9189BB71E7B}">
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C0C399-15A2-4054-BE38-EFE0308DA1A2}">
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="26.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>131</v>
+      </c>
+      <c r="B12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>131</v>
+      </c>
+      <c r="B16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>155</v>
+      </c>
+      <c r="B33" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>155</v>
+      </c>
+      <c r="B34" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>155</v>
+      </c>
+      <c r="B35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>155</v>
+      </c>
+      <c r="B37" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>166</v>
+      </c>
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>166</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>166</v>
+      </c>
+      <c r="B45" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>166</v>
+      </c>
+      <c r="B48" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>166</v>
+      </c>
+      <c r="B49" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>166</v>
+      </c>
+      <c r="B50" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>166</v>
+      </c>
+      <c r="B51" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>166</v>
+      </c>
+      <c r="B52" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>165</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86F7D49D-FC4F-438B-AE4B-40B32B4CF7EC}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="15.75" customWidth="1"/>
   </cols>
@@ -1124,35 +2381,90 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>66</v>
+      <c r="B5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1161,12 +2473,106 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D6"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926E49B6-103C-4AB1-A361-9B56F33E0D6F}">
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
@@ -1188,64 +2594,117 @@
     </row>
     <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B6" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>61</v>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1254,14 +2713,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
   </cols>
@@ -1274,7 +2733,7 @@
         <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -1285,52 +2744,48 @@
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="2">
-        <v>100000</v>
-      </c>
-      <c r="D2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="9">
+        <v>1000000000</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>63</v>
-      </c>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="3">
-        <v>100000</v>
-      </c>
-      <c r="D3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1000000000</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="2">
-        <v>500000</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>64</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="C4" s="9">
+        <v>500000000</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1338,36 +2793,88 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B4"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D06B3A1-D745-428A-8F32-61405E6F413C}">
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="25.4140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1">
-        <v>11</v>
+      <c r="A1" t="s">
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>87</v>
+      </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>87</v>
+      </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -1,30 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\lbh00\OneDrive\문서\감사\감사자료\audit-automation\journal_analyzer\sejoong\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EB5788A-30F6-462E-87B6-86869ED1C49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9B5B92-2AD5-4A8B-BCDB-72DD0EA3CE04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" r:id="rId2"/>
     <sheet name="심층분석 (계정별 Top) " sheetId="9" r:id="rId3"/>
     <sheet name="총계정원장" sheetId="10" r:id="rId4"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="6" r:id="rId5"/>
-    <sheet name="상대계정 분석" sheetId="7" r:id="rId6"/>
-    <sheet name="벤포드 분석" sheetId="3" r:id="rId7"/>
-    <sheet name="라운드넘버 분석" sheetId="4" r:id="rId8"/>
-    <sheet name="매출 vs 비용 교차" sheetId="8" r:id="rId9"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="11" r:id="rId10"/>
-    <sheet name="1" sheetId="12" r:id="rId11"/>
-    <sheet name="특수관계자 분석" sheetId="5" r:id="rId12"/>
+    <sheet name="상대계정 분석" sheetId="7" r:id="rId5"/>
+    <sheet name="벤포드 분석" sheetId="3" r:id="rId6"/>
+    <sheet name="라운드넘버 분석" sheetId="4" r:id="rId7"/>
+    <sheet name="매출 vs 비용 교차" sheetId="8" r:id="rId8"/>
+    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="11" r:id="rId9"/>
+    <sheet name="특수관계자 분석" sheetId="5" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="173">
   <si>
     <t>분석번호</t>
   </si>
@@ -58,543 +56,550 @@
     <t>실행여부</t>
   </si>
   <si>
+    <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>전체</t>
+  </si>
+  <si>
+    <t>벤포드 분석</t>
+  </si>
+  <si>
+    <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분석 시트 참조</t>
+  </si>
+  <si>
+    <t>당기</t>
+  </si>
+  <si>
+    <t>데이터 개요</t>
+  </si>
+  <si>
+    <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>계정명 리스트</t>
+  </si>
+  <si>
+    <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
+  </si>
+  <si>
+    <t>사원별 집계</t>
+  </si>
+  <si>
+    <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
+  </si>
+  <si>
+    <t>일자차이 분석</t>
+  </si>
+  <si>
+    <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분석 시트 참조</t>
+  </si>
+  <si>
+    <t>상대계정 분석</t>
+  </si>
+  <si>
+    <t>특정 계정의 상대계정 분석 → 상대계정분석 시트 참조</t>
+  </si>
+  <si>
+    <t>키워드 검색</t>
+  </si>
+  <si>
+    <t>적요 키워드 검색 → 키워드검색 시트 참조</t>
+  </si>
+  <si>
+    <t>라운드넘버 분석</t>
+  </si>
+  <si>
+    <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
+  </si>
+  <si>
+    <t>특수관계자 분석</t>
+  </si>
+  <si>
+    <t>특수관계자 거래처 거래 추출 → 특수관계자 시트 참조</t>
+  </si>
+  <si>
+    <t>자산 vs 부채 교차</t>
+  </si>
+  <si>
+    <t>자산/부채 동시 발생 거래처 분석</t>
+  </si>
+  <si>
+    <t>매출 vs 비용 교차</t>
+  </si>
+  <si>
+    <t>매출/비용 동시 발생 거래처 분석</t>
+  </si>
+  <si>
+    <t>심층분석 (계정별 Top)</t>
+  </si>
+  <si>
+    <t>계정별 거래처 Top N 추출 → 심층분석 시트 참조</t>
+  </si>
+  <si>
+    <t>AI 계정별 분석</t>
+  </si>
+  <si>
+    <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+  </si>
+  <si>
+    <t>데이터·헤더 확인</t>
+  </si>
+  <si>
+    <t>컬럼 인식 현황 점검 (파라미터 불필요)</t>
+  </si>
+  <si>
+    <t>거래처 분석</t>
+  </si>
+  <si>
+    <t>특정 거래처 복합조건 상세 분석 → 거래처분석 시트 참조</t>
+  </si>
+  <si>
+    <t>벤포드 이탈 상세 추출</t>
+  </si>
+  <si>
+    <t>벤포드 이탈 전표 상세 추출 → 벤포드이탈 시트 참조</t>
+  </si>
+  <si>
+    <t>월별 전계정 분석</t>
+  </si>
+  <si>
+    <t>전 계정 월별 차변/대변 집계 (파라미터 불필요)</t>
+  </si>
+  <si>
+    <t>항목</t>
+  </si>
+  <si>
+    <t>설정값</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>ClientName</t>
+  </si>
+  <si>
+    <t>㈜세중</t>
+  </si>
+  <si>
+    <t>StartDate</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD 형식</t>
+  </si>
+  <si>
+    <t>EndDate</t>
+  </si>
+  <si>
+    <t>TargetYear</t>
+  </si>
+  <si>
+    <t>계정과목</t>
+  </si>
+  <si>
+    <t>금액열</t>
+  </si>
+  <si>
+    <t>차변</t>
+  </si>
+  <si>
+    <t>대변</t>
+  </si>
+  <si>
+    <t>보통예금</t>
+  </si>
+  <si>
+    <t>(전체)</t>
+  </si>
+  <si>
+    <t>최소금액</t>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>별도분석시트 필요없는 분석</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>차변</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대변</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처 전기_당기 비교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>분 분석목록시트에 실행여부가 Y이고 관련분서시트가 없으면 기본분석값으로 실행</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보통예금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미수대매금(국제항공권판매)</t>
+  </si>
+  <si>
+    <t>항공권판매(국제)</t>
+  </si>
+  <si>
+    <t>외상매출금(PLM)</t>
+  </si>
+  <si>
+    <t>미수금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>미수금(기 타)</t>
+  </si>
+  <si>
+    <t>상품매출액(PLM)</t>
+  </si>
+  <si>
+    <t>용역매출액(S&amp;C)</t>
+  </si>
+  <si>
+    <t>미지급금(일반)</t>
+  </si>
+  <si>
+    <t>외상매출금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>매출액(기타항공권판매수입)</t>
+  </si>
+  <si>
+    <t>매출액(해외여행알선수입)</t>
+  </si>
+  <si>
+    <t>예수금(국제항공권환불)</t>
+  </si>
+  <si>
+    <t>미수금(국제항공취급수수료)</t>
+  </si>
+  <si>
+    <t>선급금(입체금-국내관광알선)</t>
+  </si>
+  <si>
+    <t>선수금(국제항공권)</t>
+  </si>
+  <si>
+    <t>매출액(국제항공취급수수료)</t>
+  </si>
+  <si>
+    <t>계정과목</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>매출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상품매출액(S&amp;C)</t>
+  </si>
+  <si>
+    <t>비용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>지급수수료(S&amp;C)</t>
+  </si>
+  <si>
+    <t>지급수수료(PLM)</t>
+  </si>
+  <si>
+    <t>접대비</t>
+  </si>
+  <si>
+    <t>㈜세중샤론손해보험</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대표이사</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜세중엔지니어링</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(재)우리옛돌문화재단</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜세중인터내셔널</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>㈜세성항운</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천신일</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천세전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천호전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>천미전</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>잔액증감분석 (계정별 거래처별)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 계정별 거래처별로 기초잔액 증가 감소 기말 잔액 추출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>선급금(보험가입대급금)</t>
+  </si>
+  <si>
+    <t>선급금(에스앤씨)</t>
+  </si>
+  <si>
+    <t>선급금(여권및비자대)</t>
+  </si>
+  <si>
+    <t>선급금(일반)</t>
+  </si>
+  <si>
+    <t>선급금(입체금-해외여행알선)</t>
+  </si>
+  <si>
+    <t>미수금(국내관광알선)</t>
+  </si>
+  <si>
+    <t>미수금(국내항공권-정산)</t>
+  </si>
+  <si>
+    <t>미수금(국내항공취급수수료)</t>
+  </si>
+  <si>
+    <t>미수금(국제항공권-정산)</t>
+  </si>
+  <si>
+    <t>미수금(기타)</t>
+  </si>
+  <si>
+    <t>미수금(에스앤씨)</t>
+  </si>
+  <si>
+    <t>미수금(여권비자취급수수료)</t>
+  </si>
+  <si>
+    <t>미수금(정보기술)</t>
+  </si>
+  <si>
+    <t>미수금(카드판매)</t>
+  </si>
+  <si>
+    <t>미수금(해외여행환불)</t>
+  </si>
+  <si>
+    <t>미수금(호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>미수대매금(국내항공권판매)</t>
+  </si>
+  <si>
+    <t>미수대매금(국제항공권판매 ADM)</t>
+  </si>
+  <si>
+    <t>단기대여금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>장기대여금</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래처명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>총계정원장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기/당기/전당기 기간의 게정별 월별합계 차/대/전체로 추출</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가수금</t>
+  </si>
+  <si>
+    <t>자산</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>미수금환불(국제항공)</t>
+  </si>
+  <si>
+    <t>정기예금</t>
+  </si>
+  <si>
+    <t>수탁금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>투자매도가능증권</t>
+  </si>
+  <si>
+    <t>상품(PLM)</t>
+  </si>
+  <si>
+    <t>상품(S&amp;C)</t>
+  </si>
+  <si>
+    <t>수탁금(호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>선급금(입체금-호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>선급금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>정기성예금</t>
+  </si>
+  <si>
+    <t>장기대여금</t>
+  </si>
+  <si>
+    <t>미수수익</t>
+  </si>
+  <si>
+    <t>외화예금</t>
+  </si>
+  <si>
+    <t>미지급금(국제항공권-정산)</t>
+  </si>
+  <si>
+    <t>선수금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>외상매입금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>미지급금(해외여행알선)</t>
+  </si>
+  <si>
+    <t>외상매입금(PLM)</t>
+  </si>
+  <si>
+    <t>미지급금(호텔콘도판매)</t>
+  </si>
+  <si>
+    <t>미지급금(S&amp;C)</t>
+  </si>
+  <si>
+    <t>예수금(결산)</t>
+  </si>
+  <si>
+    <t>미지급금(회사카드사용분-단체)</t>
+  </si>
+  <si>
+    <t>예수금(갑근세)</t>
+  </si>
+  <si>
+    <t>부채</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항공권판매(국제항공취급수수료)</t>
+  </si>
+  <si>
+    <t>매출액(해외호텔알선수입)</t>
+  </si>
+  <si>
+    <t>용역매출액(PLM)</t>
+  </si>
+  <si>
+    <t>매출액(국내관광알선수입)</t>
+  </si>
+  <si>
+    <t>매출액(국제항공권판매수입)</t>
+  </si>
+  <si>
+    <t>매출액(여권비자취급수수료)</t>
+  </si>
+  <si>
+    <t>매출액(국내호텔콘도알선수입)</t>
+  </si>
+  <si>
+    <t>매출액(기타)</t>
+  </si>
+  <si>
+    <t>매출액(국내항공취급수수료)</t>
+  </si>
+  <si>
+    <t>매출액(국내항공권판매수입)</t>
+  </si>
+  <si>
+    <t>매출액</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>은행조회서 완전성</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이자비용, 장단기차입금, 전환사채, RCPS등의 거래처와 은행조회서 발송내역 비교</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>당기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4,5,6,16,19,22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>계정별 상세거래내역</t>
+  </si>
+  <si>
+    <t>각 계정별로 계정과목 차변/대변/차변대변모두 를 선택하여 데어터추출</t>
+  </si>
+  <si>
+    <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있어도 분석실행 안 됨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>분석대상</t>
-  </si>
-  <si>
-    <t>전기/당기 거래처별 금액 비교 → 거래처비교 시트 참조</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>전체</t>
-  </si>
-  <si>
-    <t>벤포드 분석</t>
-  </si>
-  <si>
-    <t>첫째자리 빈도 벤포드 기댓값 비교 → 벤포드분석 시트 참조</t>
-  </si>
-  <si>
-    <t>당기</t>
-  </si>
-  <si>
-    <t>데이터 개요</t>
-  </si>
-  <si>
-    <t>전체 데이터 건수/금액 요약 (파라미터 불필요)</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>계정명 리스트</t>
-  </si>
-  <si>
-    <t>계정명 목록 및 금액 통계 (파라미터 불필요)</t>
-  </si>
-  <si>
-    <t>사원별 집계</t>
-  </si>
-  <si>
-    <t>사원별 차변/대변 계정 집계 (파라미터 불필요)</t>
-  </si>
-  <si>
-    <t>일자차이 분석</t>
-  </si>
-  <si>
-    <t>전표일자 vs 등록일자 N일 이상 지연 전표 → 일자차이분석 시트 참조</t>
-  </si>
-  <si>
-    <t>상대계정 분석</t>
-  </si>
-  <si>
-    <t>특정 계정의 상대계정 분석 → 상대계정분석 시트 참조</t>
-  </si>
-  <si>
-    <t>키워드 검색</t>
-  </si>
-  <si>
-    <t>적요 키워드 검색 → 키워드검색 시트 참조</t>
-  </si>
-  <si>
-    <t>라운드넘버 분석</t>
-  </si>
-  <si>
-    <t>특정 배수 단위 금액 탐지 → 라운드넘버 시트 참조</t>
-  </si>
-  <si>
-    <t>특수관계자 분석</t>
-  </si>
-  <si>
-    <t>특수관계자 거래처 거래 추출 → 특수관계자 시트 참조</t>
-  </si>
-  <si>
-    <t>자산 vs 부채 교차</t>
-  </si>
-  <si>
-    <t>자산/부채 동시 발생 거래처 분석</t>
-  </si>
-  <si>
-    <t>매출 vs 비용 교차</t>
-  </si>
-  <si>
-    <t>매출/비용 동시 발생 거래처 분석</t>
-  </si>
-  <si>
-    <t>심층분석 (계정별 Top)</t>
-  </si>
-  <si>
-    <t>계정별 거래처 Top N 추출 → 심층분석 시트 참조</t>
-  </si>
-  <si>
-    <t>AI 계정별 분석</t>
-  </si>
-  <si>
-    <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
-  </si>
-  <si>
-    <t>데이터·헤더 확인</t>
-  </si>
-  <si>
-    <t>컬럼 인식 현황 점검 (파라미터 불필요)</t>
-  </si>
-  <si>
-    <t>거래처 분석</t>
-  </si>
-  <si>
-    <t>특정 거래처 복합조건 상세 분석 → 거래처분석 시트 참조</t>
-  </si>
-  <si>
-    <t>벤포드 이탈 상세 추출</t>
-  </si>
-  <si>
-    <t>벤포드 이탈 전표 상세 추출 → 벤포드이탈 시트 참조</t>
-  </si>
-  <si>
-    <t>월별 전계정 분석</t>
-  </si>
-  <si>
-    <t>전 계정 월별 차변/대변 집계 (파라미터 불필요)</t>
-  </si>
-  <si>
-    <t>항목</t>
-  </si>
-  <si>
-    <t>설정값</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>ClientName</t>
-  </si>
-  <si>
-    <t>㈜세중</t>
-  </si>
-  <si>
-    <t>StartDate</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD 형식</t>
-  </si>
-  <si>
-    <t>EndDate</t>
-  </si>
-  <si>
-    <t>TargetYear</t>
-  </si>
-  <si>
-    <t>계정과목</t>
-  </si>
-  <si>
-    <t>금액열</t>
-  </si>
-  <si>
-    <t>차변</t>
-  </si>
-  <si>
-    <t>대변</t>
-  </si>
-  <si>
-    <t>보통예금</t>
-  </si>
-  <si>
-    <t>(전체)</t>
-  </si>
-  <si>
-    <t>최소금액</t>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>별도분석시트 필요없는 분석</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있었도 분석실행 안 됨</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>차변</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대변</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래처 전기_당기 비교</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>분 분석목록시트에 실행여부가 Y이고 관련분서시트가 없으면 기본분석값으로 실행</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>계정명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>구분</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>보통예금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미수대매금(국제항공권판매)</t>
-  </si>
-  <si>
-    <t>항공권판매(국제)</t>
-  </si>
-  <si>
-    <t>외상매출금(PLM)</t>
-  </si>
-  <si>
-    <t>미수금(해외여행알선)</t>
-  </si>
-  <si>
-    <t>미수금(기 타)</t>
-  </si>
-  <si>
-    <t>상품매출액(PLM)</t>
-  </si>
-  <si>
-    <t>용역매출액(S&amp;C)</t>
-  </si>
-  <si>
-    <t>미지급금(일반)</t>
-  </si>
-  <si>
-    <t>외상매출금(S&amp;C)</t>
-  </si>
-  <si>
-    <t>매출액(기타항공권판매수입)</t>
-  </si>
-  <si>
-    <t>매출액(해외여행알선수입)</t>
-  </si>
-  <si>
-    <t>예수금(국제항공권환불)</t>
-  </si>
-  <si>
-    <t>미수금(국제항공취급수수료)</t>
-  </si>
-  <si>
-    <t>선급금(입체금-국내관광알선)</t>
-  </si>
-  <si>
-    <t>선수금(국제항공권)</t>
-  </si>
-  <si>
-    <t>매출액(국제항공취급수수료)</t>
-  </si>
-  <si>
-    <t>계정과목</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>매출</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>상품매출액(S&amp;C)</t>
-  </si>
-  <si>
-    <t>비용</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>지급수수료(S&amp;C)</t>
-  </si>
-  <si>
-    <t>지급수수료(PLM)</t>
-  </si>
-  <si>
-    <t>접대비</t>
-  </si>
-  <si>
-    <t>㈜세중샤론손해보험</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대표이사</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>㈜세중엔지니어링</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>(재)우리옛돌문화재단</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>㈜세중인터내셔널</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>㈜세성항운</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>천신일</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>천세전</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>천호전</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>천미전</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>잔액증감분석 (계정별 거래처별)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>각 계정별 거래처별로 기초잔액 증가 감소 기말 잔액 추출</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>계저영</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>선급금(보험가입대급금)</t>
-  </si>
-  <si>
-    <t>선급금(에스앤씨)</t>
-  </si>
-  <si>
-    <t>선급금(여권및비자대)</t>
-  </si>
-  <si>
-    <t>선급금(일반)</t>
-  </si>
-  <si>
-    <t>선급금(입체금-해외여행알선)</t>
-  </si>
-  <si>
-    <t>미수금(국내관광알선)</t>
-  </si>
-  <si>
-    <t>미수금(국내항공권-정산)</t>
-  </si>
-  <si>
-    <t>미수금(국내항공취급수수료)</t>
-  </si>
-  <si>
-    <t>미수금(국제항공권-정산)</t>
-  </si>
-  <si>
-    <t>미수금(기타)</t>
-  </si>
-  <si>
-    <t>미수금(에스앤씨)</t>
-  </si>
-  <si>
-    <t>미수금(여권비자취급수수료)</t>
-  </si>
-  <si>
-    <t>미수금(정보기술)</t>
-  </si>
-  <si>
-    <t>미수금(카드판매)</t>
-  </si>
-  <si>
-    <t>미수금(해외여행환불)</t>
-  </si>
-  <si>
-    <t>미수금(호텔콘도판매)</t>
-  </si>
-  <si>
-    <t>미수대매금(국내항공권판매)</t>
-  </si>
-  <si>
-    <t>미수대매금(국제항공권판매 ADM)</t>
-  </si>
-  <si>
-    <t>단기대여금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>장기대여금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래처명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>총계정원장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전기/당기/전당기 기간의 게정별 월별합계 차/대/전체로 추출</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가수금</t>
-  </si>
-  <si>
-    <t>자산</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>미수금환불(국제항공)</t>
-  </si>
-  <si>
-    <t>정기예금</t>
-  </si>
-  <si>
-    <t>수탁금(해외여행알선)</t>
-  </si>
-  <si>
-    <t>투자매도가능증권</t>
-  </si>
-  <si>
-    <t>상품(PLM)</t>
-  </si>
-  <si>
-    <t>상품(S&amp;C)</t>
-  </si>
-  <si>
-    <t>수탁금(호텔콘도판매)</t>
-  </si>
-  <si>
-    <t>선급금(입체금-호텔콘도판매)</t>
-  </si>
-  <si>
-    <t>선급금(S&amp;C)</t>
-  </si>
-  <si>
-    <t>정기성예금</t>
-  </si>
-  <si>
-    <t>장기대여금</t>
-  </si>
-  <si>
-    <t>미수수익</t>
-  </si>
-  <si>
-    <t>외화예금</t>
-  </si>
-  <si>
-    <t>미지급금(국제항공권-정산)</t>
-  </si>
-  <si>
-    <t>선수금(해외여행알선)</t>
-  </si>
-  <si>
-    <t>외상매입금(S&amp;C)</t>
-  </si>
-  <si>
-    <t>미지급금(해외여행알선)</t>
-  </si>
-  <si>
-    <t>외상매입금(PLM)</t>
-  </si>
-  <si>
-    <t>미지급금(호텔콘도판매)</t>
-  </si>
-  <si>
-    <t>미지급금(S&amp;C)</t>
-  </si>
-  <si>
-    <t>예수금(결산)</t>
-  </si>
-  <si>
-    <t>미지급금(회사카드사용분-단체)</t>
-  </si>
-  <si>
-    <t>예수금(갑근세)</t>
-  </si>
-  <si>
-    <t>부채</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>항공권판매(국제항공취급수수료)</t>
-  </si>
-  <si>
-    <t>매출액(해외호텔알선수입)</t>
-  </si>
-  <si>
-    <t>용역매출액(PLM)</t>
-  </si>
-  <si>
-    <t>매출액(국내관광알선수입)</t>
-  </si>
-  <si>
-    <t>매출액(국제항공권판매수입)</t>
-  </si>
-  <si>
-    <t>매출액(여권비자취급수수료)</t>
-  </si>
-  <si>
-    <t>매출액(국내호텔콘도알선수입)</t>
-  </si>
-  <si>
-    <t>매출액(기타)</t>
-  </si>
-  <si>
-    <t>매출액(국내항공취급수수료)</t>
-  </si>
-  <si>
-    <t>매출액(국내항공권판매수입)</t>
-  </si>
-  <si>
-    <t>매출액</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>은행조회서 완전성</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이자비용, 장단기차입금, 전환사채, RCPS등의 거래처와 은행조회서 발송내역 비교</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>당기</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4,5,6,16,19,22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그룹기준열</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>전표번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1061,38 +1066,38 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4">
         <v>46023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="5">
         <v>46387</v>
@@ -1101,7 +1106,7 @@
     </row>
     <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>2026</v>
@@ -1115,235 +1120,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D312E48-8E6E-493E-8A48-BE945225BF96}">
-  <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="30.58203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>118</v>
-      </c>
-      <c r="B18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>121</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>122</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA246E49-9EB8-4E4E-9005-B617F351DDBE}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -1353,7 +1129,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
         <v>3</v>
@@ -1361,82 +1137,82 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
@@ -1450,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1473,8 +1249,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
+      <c r="E1" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
@@ -1482,16 +1258,16 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
@@ -1499,16 +1275,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
@@ -1516,16 +1292,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
@@ -1533,16 +1309,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
@@ -1550,16 +1326,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
@@ -1567,16 +1343,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -1584,16 +1360,16 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
         <v>20</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
       <c r="D8" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -1601,16 +1377,16 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -1618,16 +1394,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -1635,16 +1411,16 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
         <v>26</v>
       </c>
-      <c r="C11" t="s">
-        <v>27</v>
-      </c>
       <c r="D11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" t="s">
         <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -1652,16 +1428,16 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
-        <v>29</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -1669,16 +1445,16 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
       <c r="D13" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
@@ -1686,16 +1462,16 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
       <c r="D14" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -1703,16 +1479,16 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
         <v>34</v>
       </c>
-      <c r="C15" t="s">
-        <v>35</v>
-      </c>
       <c r="D15" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -1720,16 +1496,16 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
       <c r="D16" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
@@ -1737,16 +1513,16 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
       </c>
-      <c r="C17" t="s">
-        <v>39</v>
-      </c>
       <c r="D17" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
@@ -1754,16 +1530,16 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
         <v>40</v>
       </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
@@ -1771,16 +1547,16 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
         <v>42</v>
       </c>
-      <c r="C19" t="s">
-        <v>43</v>
-      </c>
       <c r="D19" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
@@ -1788,16 +1564,16 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
@@ -1805,16 +1581,16 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
@@ -1822,34 +1598,51 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="8">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
         <v>167</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>168</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D23" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
         <v>60</v>
       </c>
-      <c r="E22" t="s">
+      <c r="C29" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>66</v>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1868,47 +1661,47 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1927,426 +1720,426 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" t="s">
         <v>131</v>
-      </c>
-      <c r="B11" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B37" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B40" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B43" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B44" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B48" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B49" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B52" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B53" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2356,115 +2149,154 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86F7D49D-FC4F-438B-AE4B-40B32B4CF7EC}">
-  <dimension ref="A1:D9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926E49B6-103C-4AB1-A361-9B56F33E0D6F}">
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>79</v>
-      </c>
       <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="C8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2474,100 +2306,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926E49B6-103C-4AB1-A361-9B56F33E0D6F}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="25.4140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -2580,131 +2318,131 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2713,7 +2451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -2727,63 +2465,63 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" s="9">
         <v>1000000000</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="10">
         <v>1000000000</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" s="9">
         <v>500000000</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -2793,7 +2531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D06B3A1-D745-428A-8F32-61405E6F413C}">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -2803,74 +2541,288 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
         <v>89</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D312E48-8E6E-493E-8A48-BE945225BF96}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="30.58203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>108</v>
+      </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -18,7 +18,7 @@
     <sheet name="특수관계자 분석" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="은행조회서 완전성" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="거래처 분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="손익항목분析" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="손익월별분析" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -84,6 +84,42 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <i val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <i val="1"/>
       <color rgb="00375623"/>
       <sz val="9"/>
@@ -99,7 +135,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -133,6 +169,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
@@ -142,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -193,6 +239,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
@@ -215,7 +276,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -268,19 +329,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -288,6 +336,38 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -660,12 +740,12 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="19" min="1" max="1"/>
-    <col width="22" customWidth="1" style="19" min="2" max="2"/>
-    <col width="30" customWidth="1" style="19" min="3" max="3"/>
+    <col width="18" customWidth="1" style="25" min="1" max="1"/>
+    <col width="22" customWidth="1" style="25" min="2" max="2"/>
+    <col width="30" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="19">
+    <row r="1" ht="18" customHeight="1" s="25">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
@@ -682,7 +762,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="19">
+    <row r="2" ht="16" customHeight="1" s="25">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ClientName</t>
@@ -695,7 +775,7 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="19">
+    <row r="3" ht="16" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>StartDate</t>
@@ -710,7 +790,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="19">
+    <row r="4" ht="16" customHeight="1" s="25">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EndDate</t>
@@ -721,7 +801,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1" s="19">
+    <row r="5" ht="16" customHeight="1" s="25">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TargetYear</t>
@@ -746,7 +826,7 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18.25" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
+    <col width="18.25" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,7 +978,7 @@
   <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="20.25" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
+    <col width="20.25" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,20 +1136,20 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="19" min="1" max="1"/>
-    <col width="25" customWidth="1" style="19" min="2" max="2"/>
-    <col width="35" customWidth="1" style="19" min="3" max="3"/>
-    <col width="10" customWidth="1" style="19" min="4" max="5"/>
+    <col width="18" customWidth="1" style="25" min="1" max="1"/>
+    <col width="25" customWidth="1" style="25" min="2" max="2"/>
+    <col width="35" customWidth="1" style="25" min="3" max="3"/>
+    <col width="10" customWidth="1" style="25" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="19">
-      <c r="A1" s="18" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="25">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="19">
+    <row r="2" ht="20" customHeight="1" s="25">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>작업명</t>
@@ -1096,7 +1176,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="19">
+    <row r="3" ht="18" customHeight="1" s="25">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>분석01</t>
@@ -1123,7 +1203,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="19">
+    <row r="4" ht="18" customHeight="1" s="25">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>분석02</t>
@@ -1150,7 +1230,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="19">
+    <row r="5" ht="18" customHeight="1" s="25">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>분석03</t>
@@ -1177,7 +1257,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="19">
+    <row r="6" ht="18" customHeight="1" s="25">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>분석04</t>
@@ -1200,7 +1280,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="19">
+    <row r="7" ht="18" customHeight="1" s="25">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>분석05</t>
@@ -1219,35 +1299,35 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="19">
+    <row r="8" ht="18" customHeight="1" s="25">
       <c r="A8" s="16" t="n"/>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="19">
+    <row r="9" ht="18" customHeight="1" s="25">
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="19">
+    <row r="10" ht="18" customHeight="1" s="25">
       <c r="A10" s="16" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="19">
+    <row r="11" ht="18" customHeight="1" s="25">
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="17" t="n"/>
       <c r="E11" s="17" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="19">
+    <row r="12" ht="18" customHeight="1" s="25">
       <c r="A12" s="16" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n"/>
@@ -1272,144 +1352,144 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" style="19" min="1" max="1"/>
-    <col width="10" customWidth="1" style="19" min="2" max="2"/>
-    <col width="10" customWidth="1" style="19" min="3" max="3"/>
+    <col width="25" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="10" customWidth="1" style="25" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="19">
-      <c r="A1" s="22" t="inlineStr">
-        <is>
-          <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="19">
-      <c r="A2" s="23" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="25">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리 | 거래처별 비교는 2번 메뉴 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="25">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B2" s="23" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="19">
-      <c r="A3" s="24" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="25">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="25" t="inlineStr">
+      <c r="C3" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="19">
-      <c r="A4" s="24" t="inlineStr">
+    <row r="4" ht="18" customHeight="1" s="25">
+      <c r="A4" s="31" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="19">
-      <c r="A5" s="24" t="inlineStr">
+    <row r="5" ht="18" customHeight="1" s="25">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>판매비와관리비</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="19">
-      <c r="A6" s="24" t="inlineStr">
+    <row r="6" ht="18" customHeight="1" s="25">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>영업외수익</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="19">
-      <c r="A7" s="24" t="inlineStr">
+    <row r="7" ht="18" customHeight="1" s="25">
+      <c r="A7" s="31" t="inlineStr">
         <is>
           <t>영업외비용</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="19">
-      <c r="A8" s="24" t="inlineStr"/>
-      <c r="B8" s="25" t="inlineStr"/>
-      <c r="C8" s="25" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="19">
-      <c r="A9" s="24" t="inlineStr"/>
-      <c r="B9" s="25" t="inlineStr"/>
-      <c r="C9" s="25" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="19">
-      <c r="A10" s="24" t="inlineStr"/>
-      <c r="B10" s="25" t="inlineStr"/>
-      <c r="C10" s="25" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="19">
-      <c r="A11" s="24" t="inlineStr"/>
-      <c r="B11" s="25" t="inlineStr"/>
-      <c r="C11" s="25" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="19">
-      <c r="A12" s="24" t="inlineStr"/>
-      <c r="B12" s="25" t="inlineStr"/>
-      <c r="C12" s="25" t="inlineStr"/>
+    <row r="8" ht="18" customHeight="1" s="25">
+      <c r="A8" s="31" t="inlineStr"/>
+      <c r="B8" s="32" t="inlineStr"/>
+      <c r="C8" s="32" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="25">
+      <c r="A9" s="31" t="inlineStr"/>
+      <c r="B9" s="32" t="inlineStr"/>
+      <c r="C9" s="32" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="25">
+      <c r="A10" s="31" t="inlineStr"/>
+      <c r="B10" s="32" t="inlineStr"/>
+      <c r="C10" s="32" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="25">
+      <c r="A11" s="31" t="inlineStr"/>
+      <c r="B11" s="32" t="inlineStr"/>
+      <c r="C11" s="32" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="25">
+      <c r="A12" s="31" t="inlineStr"/>
+      <c r="B12" s="32" t="inlineStr"/>
+      <c r="C12" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1425,17 +1505,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="12" customWidth="1" style="19" min="1" max="1"/>
-    <col width="27.83203125" customWidth="1" style="19" min="2" max="2"/>
-    <col width="72.5" bestFit="1" customWidth="1" style="19" min="3" max="3"/>
-    <col width="12" customWidth="1" style="19" min="4" max="4"/>
-    <col width="21.6640625" bestFit="1" customWidth="1" style="19" min="6" max="6"/>
+    <col width="12" customWidth="1" style="25" min="1" max="1"/>
+    <col width="27.83203125" customWidth="1" style="25" min="2" max="2"/>
+    <col width="72.5" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
+    <col width="12" customWidth="1" style="25" min="4" max="4"/>
+    <col width="21.6640625" bestFit="1" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="19">
+    <row r="1" ht="18" customHeight="1" s="25">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>분석번호</t>
@@ -1462,7 +1542,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="19">
+    <row r="2" ht="16" customHeight="1" s="25">
       <c r="A2" s="6" t="n">
         <v>2</v>
       </c>
@@ -1487,7 +1567,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="19">
+    <row r="3" ht="16" customHeight="1" s="25">
       <c r="A3" s="7" t="n">
         <v>3</v>
       </c>
@@ -1512,7 +1592,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="19">
+    <row r="4" ht="16" customHeight="1" s="25">
       <c r="A4" s="6" t="n">
         <v>4</v>
       </c>
@@ -1537,7 +1617,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="19">
+    <row r="5" ht="16" customHeight="1" s="25">
       <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
@@ -1562,7 +1642,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="19">
+    <row r="6" ht="16" customHeight="1" s="25">
       <c r="A6" s="6" t="n">
         <v>6</v>
       </c>
@@ -1587,7 +1667,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="19">
+    <row r="7" ht="16" customHeight="1" s="25">
       <c r="A7" s="7" t="n">
         <v>7</v>
       </c>
@@ -2012,59 +2092,81 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>리스완전성</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>25</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>손익월별분析</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>손익 계정별 전기/당기 차변·대변 선택 비교 (월별 + 거래처별)</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>별도분석시트 필요없는 분석</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>4,5,6,16,19,22</t>
-        </is>
-      </c>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있어도 분석실행 안 됨</t>
+          <t>별도분석시트 필요없는 분석</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
+          <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있어도 분석실행 안 됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
           <t>분 분석목록시트에 실행여부가 Y이고 관련분서시트가 없으면 기본분석값으로 실행</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>손익항목분析</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>손익 계정별 전기/당기 차변·대변 선택 비교 (월별 + 거래처별)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>전체</t>
+    <row r="33"/>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4,5,6,16,19,22</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2184,7 @@
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2162,7 +2264,7 @@
   <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="26.1640625" bestFit="1" customWidth="1" style="19" min="2" max="2"/>
+    <col width="26.1640625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2815,7 +2917,7 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3057,13 +3159,13 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
-    <col width="10" customWidth="1" style="19" min="2" max="2"/>
-    <col width="12" customWidth="1" style="19" min="3" max="3"/>
-    <col width="42" customWidth="1" style="19" min="4" max="4"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="12" customWidth="1" style="25" min="3" max="3"/>
+    <col width="42" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="19">
+    <row r="1" ht="18" customHeight="1" s="25">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -3085,7 +3187,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="19">
+    <row r="2" ht="16" customHeight="1" s="25">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>미수대매금(국제항공권판매)</t>
@@ -3103,7 +3205,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="19">
+    <row r="3" ht="16" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>외상매출금(S&amp;C)</t>
@@ -3121,7 +3223,7 @@
       </c>
       <c r="D3" s="3" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1" s="19">
+    <row r="4" ht="16" customHeight="1" s="25">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>미수금(해외여행알선)</t>
@@ -3156,7 +3258,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="19">
+    <row r="6" ht="16" customHeight="1" s="25">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>보통예금</t>
@@ -3174,7 +3276,7 @@
       </c>
       <c r="D6" s="13" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1" s="19">
+    <row r="7" ht="16" customHeight="1" s="25">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>예수금(국제항공권환불)</t>
@@ -3274,14 +3376,14 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" style="19" min="1" max="1"/>
-    <col width="10" customWidth="1" style="19" min="2" max="2"/>
-    <col width="16.6640625" customWidth="1" style="19" min="3" max="3"/>
-    <col width="12" customWidth="1" style="19" min="4" max="4"/>
-    <col width="36" customWidth="1" style="19" min="5" max="5"/>
+    <col width="16" customWidth="1" style="25" min="1" max="1"/>
+    <col width="10" customWidth="1" style="25" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" style="25" min="3" max="3"/>
+    <col width="12" customWidth="1" style="25" min="4" max="4"/>
+    <col width="36" customWidth="1" style="25" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="19">
+    <row r="1" ht="18" customHeight="1" s="25">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -3308,7 +3410,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="19">
+    <row r="2" ht="16" customHeight="1" s="25">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -3319,7 +3421,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="27" t="n">
         <v>1000000000</v>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -3329,7 +3431,7 @@
       </c>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="19">
+    <row r="3" ht="16" customHeight="1" s="25">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -3340,7 +3442,7 @@
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="21" t="n">
+      <c r="C3" s="28" t="n">
         <v>1000000000</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -3350,7 +3452,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1" s="19">
+    <row r="4" ht="16" customHeight="1" s="25">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>보통예금</t>
@@ -3361,7 +3463,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="27" t="n">
         <v>500000000</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -3385,7 +3487,7 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="19" min="2" max="2"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3510,7 +3612,7 @@
   <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30.58203125" bestFit="1" customWidth="1" style="19" min="1" max="1"/>
+    <col width="30.58203125" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -135,7 +135,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -185,6 +185,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -276,7 +281,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -368,6 +373,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1505,14 +1513,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" style="25" min="1" max="1"/>
     <col width="27.83203125" customWidth="1" style="25" min="2" max="2"/>
     <col width="72.5" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
     <col width="12" customWidth="1" style="25" min="4" max="4"/>
-    <col width="21.6640625" bestFit="1" customWidth="1" style="25" min="6" max="6"/>
+    <col width="8" bestFit="1" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="25">
@@ -1541,6 +1549,11 @@
           <t>분석대상</t>
         </is>
       </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>기준월</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16" customHeight="1" s="25">
       <c r="A2" s="6" t="n">
@@ -2137,10 +2150,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
@@ -2162,7 +2171,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -3,22 +3,26 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="심층분석 (계정별 Top) " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="총계정원장" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="상대계정 분석" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="벤포드 분석" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="라운드넘버 분석" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="매출 vs 비용 교차" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="특수관계자 분석" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="은행조회서 완전성" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="거래처 분석" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="손익월별분析" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="AI 계정별 분석" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AI계정별분석_실행" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="거래처 전기_당기 비교" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="심층분석 (계정별 Top) " sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="총계정원장" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="상대계정 분석" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="벤포드 분석" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="라운드넘버 분석" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="매출 vs 비용 교차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="특수관계자 분석" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="거래처 분석" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="감가상각_평가손익분석" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -30,7 +34,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="11">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -107,35 +111,12 @@
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="3"/>
-      <color theme="1"/>
-      <sz val="9"/>
+      <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <i val="1"/>
-      <color rgb="00375623"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -179,21 +160,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -257,20 +228,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
@@ -281,7 +238,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -343,40 +300,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -748,12 +696,12 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="25" min="1" max="1"/>
-    <col width="22" customWidth="1" style="25" min="2" max="2"/>
-    <col width="30" customWidth="1" style="25" min="3" max="3"/>
+    <col width="18" customWidth="1" style="26" min="1" max="1"/>
+    <col width="22" customWidth="1" style="26" min="2" max="2"/>
+    <col width="30" customWidth="1" style="26" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="25">
+    <row r="1" ht="18" customHeight="1" s="26">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
@@ -770,7 +718,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="25">
+    <row r="2" ht="16" customHeight="1" s="26">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ClientName</t>
@@ -783,7 +731,7 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="25">
+    <row r="3" ht="16" customHeight="1" s="26">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>StartDate</t>
@@ -798,7 +746,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="25">
+    <row r="4" ht="16" customHeight="1" s="26">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EndDate</t>
@@ -809,7 +757,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1" s="25">
+    <row r="5" ht="16" customHeight="1" s="26">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TargetYear</t>
@@ -831,146 +779,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18.25" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="16" customWidth="1" style="26" min="1" max="1"/>
+    <col width="10" customWidth="1" style="26" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" style="26" min="3" max="3"/>
+    <col width="12" customWidth="1" style="26" min="4" max="4"/>
+    <col width="36" customWidth="1" style="26" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="26">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>최소금액</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>㈜세중샤론손해보험</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>대표이사</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>㈜세중엔지니어링</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>(재)우리옛돌문화재단</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>㈜세중인터내셔널</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>㈜세성항운</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>천신일</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>천세전</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>천호전</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>천미전</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="8" t="n"/>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="26">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="29" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="26">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" s="30" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="26">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -983,15 +890,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="20.25" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>계정과목</t>
         </is>
       </c>
@@ -999,142 +911,875 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>단기차입금</t>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>장기차입금</t>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>매출액(국제항공취급수수료)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>유동성장기차입금</t>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>매출액(기타항공권판매수입)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전환사채</t>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>지급수수료(S&amp;C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>유동성전환사채</t>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>지급수수료(PLM)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전환상환우선주</t>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="41.9140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정영</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상매출금(항공권판매-국내항공권판매수수료)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외상매출금(항공권판매-국제항공권판매수수료)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>외상매출금(상품)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상매출금(PLM)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>외상매출금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매출금(정보기술)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>선급금(보험가입대급금)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>선급금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>유동성전환상환우선주</t>
+          <t>선급금(여권및비자대)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>선급금(일반)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>외화예금</t>
+          <t>선급금(입체금-국내관광알선)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>외화정기예금</t>
+          <t>선급금(입체금-해외여행알선)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>정기성예금</t>
+          <t>미수금(국내관광알선)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>정기예금</t>
+          <t>미수금(국내항공권-정산)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>보험료(보증보험)</t>
+          <t>미수금(국내항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>보험료(세중)</t>
+          <t>미수금(국제항공권-정산)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>보험료(세중S&amp;C)</t>
+          <t>미수금(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>보험료(자동차보험)</t>
+          <t>미수금(기타)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>보험료-기타</t>
-        </is>
-      </c>
+          <t>미수금(에스앤씨)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>미수금(여권비자취급수수료)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>미수금(정보기술)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>미수금(카드판매)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>미수금(해외여행알선)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>미수금(해외여행환불)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>미수금(호텔콘도판매)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>미수대매금(국내항공권판매)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매 ADM)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>단기대여금</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>장기대여금</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>외상매입금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>외상매입금(PLM)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>외상매입금(정보기술)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="23.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(주)세중샤론손해보험중개</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>세중엔지니어링</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(주)세중엔지니어링</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(재)우리옛돌문화재단</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>㈜세중인터내셔널</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(주)세성항운</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>(주)세중로지스틱스</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>세중인터내셔널</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>천신일</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>천세전</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>천호전</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>천미전</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="20.25" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>유동성장기부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>유동성장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>전환사채</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>유동성전환사채</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>전환상환우선주</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>유동성전환상환우선주</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>외화정기예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>정기성예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>정기예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>보험료(보증보험)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>보험료(세중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>보험료(세중S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>보험료(자동차보험)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>보험료-기타</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFED7D31"/>
@@ -1144,20 +1789,20 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="25" min="1" max="1"/>
-    <col width="25" customWidth="1" style="25" min="2" max="2"/>
-    <col width="35" customWidth="1" style="25" min="3" max="3"/>
-    <col width="10" customWidth="1" style="25" min="4" max="5"/>
+    <col width="18" customWidth="1" style="26" min="1" max="1"/>
+    <col width="25" customWidth="1" style="26" min="2" max="2"/>
+    <col width="35" customWidth="1" style="26" min="3" max="3"/>
+    <col width="10" customWidth="1" style="26" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="25">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="26">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="25">
+    <row r="2" ht="20" customHeight="1" s="26">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>작업명</t>
@@ -1184,7 +1829,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="25">
+    <row r="3" ht="18" customHeight="1" s="26">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>분석01</t>
@@ -1211,7 +1856,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="25">
+    <row r="4" ht="18" customHeight="1" s="26">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>분석02</t>
@@ -1238,7 +1883,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="25">
+    <row r="5" ht="18" customHeight="1" s="26">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>분석03</t>
@@ -1256,7 +1901,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>both</t>
         </is>
       </c>
       <c r="E5" s="17" t="inlineStr">
@@ -1265,7 +1910,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="25">
+    <row r="6" ht="18" customHeight="1" s="26">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>분석04</t>
@@ -1288,7 +1933,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="25">
+    <row r="7" ht="18" customHeight="1" s="26">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>분석05</t>
@@ -1307,35 +1952,35 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="25">
+    <row r="8" ht="18" customHeight="1" s="26">
       <c r="A8" s="16" t="n"/>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="25">
+    <row r="9" ht="18" customHeight="1" s="26">
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="25">
+    <row r="10" ht="18" customHeight="1" s="26">
       <c r="A10" s="16" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="25">
+    <row r="11" ht="18" customHeight="1" s="26">
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="17" t="n"/>
       <c r="E11" s="17" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="25">
+    <row r="12" ht="18" customHeight="1" s="26">
       <c r="A12" s="16" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n"/>
@@ -1350,159 +1995,304 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="FF70AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25" customWidth="1" style="25" min="1" max="1"/>
-    <col width="10" customWidth="1" style="25" min="2" max="2"/>
-    <col width="10" customWidth="1" style="25" min="3" max="3"/>
+    <col width="25" customWidth="1" style="26" min="1" max="1"/>
+    <col width="10" customWidth="1" style="26" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="25">
-      <c r="A1" s="29" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="26">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리 | 거래처별 비교는 2번 메뉴 사용</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="25">
-      <c r="A2" s="30" t="inlineStr">
+    <row r="2" ht="20" customHeight="1" s="26">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="C2" s="30" t="inlineStr">
+      <c r="C2" s="18" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="25">
-      <c r="A3" s="31" t="inlineStr">
-        <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B3" s="32" t="inlineStr">
+    <row r="3" ht="18" customHeight="1" s="26">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" s="25">
-      <c r="A4" s="31" t="inlineStr">
-        <is>
-          <t>매출원가</t>
-        </is>
-      </c>
-      <c r="B4" s="32" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="25">
-      <c r="A5" s="31" t="inlineStr">
-        <is>
-          <t>판매비와관리비</t>
-        </is>
-      </c>
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="25">
-      <c r="A6" s="31" t="inlineStr">
-        <is>
-          <t>영업외수익</t>
-        </is>
-      </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="26">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" s="25">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>영업외비용</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="25">
-      <c r="A8" s="31" t="inlineStr"/>
-      <c r="B8" s="32" t="inlineStr"/>
-      <c r="C8" s="32" t="inlineStr"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="25">
-      <c r="A9" s="31" t="inlineStr"/>
-      <c r="B9" s="32" t="inlineStr"/>
-      <c r="C9" s="32" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="25">
-      <c r="A10" s="31" t="inlineStr"/>
-      <c r="B10" s="32" t="inlineStr"/>
-      <c r="C10" s="32" t="inlineStr"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="25">
-      <c r="A11" s="31" t="inlineStr"/>
-      <c r="B11" s="32" t="inlineStr"/>
-      <c r="C11" s="32" t="inlineStr"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="25">
-      <c r="A12" s="31" t="inlineStr"/>
-      <c r="B12" s="32" t="inlineStr"/>
-      <c r="C12" s="32" t="inlineStr"/>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="26">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="26">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="26">
+      <c r="A7" s="19" t="n"/>
+      <c r="B7" s="20" t="n"/>
+      <c r="C7" s="20" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="26">
+      <c r="A8" s="19" t="n"/>
+      <c r="B8" s="20" t="n"/>
+      <c r="C8" s="20" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="26">
+      <c r="A9" s="19" t="n"/>
+      <c r="B9" s="20" t="n"/>
+      <c r="C9" s="20" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="26">
+      <c r="A10" s="19" t="n"/>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="26">
+      <c r="A11" s="19" t="n"/>
+      <c r="B11" s="20" t="n"/>
+      <c r="C11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="26">
+      <c r="A12" s="19" t="n"/>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="26" min="1" max="1"/>
+    <col width="10" customWidth="1" style="26" min="2" max="2"/>
+    <col width="12" customWidth="1" style="26" min="3" max="3"/>
+    <col width="10" customWidth="1" style="26" min="4" max="4"/>
+    <col width="55" customWidth="1" style="26" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외화환산손익</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융자산평가손익</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>대손상각비</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>파생상품평가손익</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1516,14 +2306,14 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="12" customWidth="1" style="25" min="1" max="1"/>
-    <col width="27.83203125" customWidth="1" style="25" min="2" max="2"/>
-    <col width="72.5" bestFit="1" customWidth="1" style="25" min="3" max="3"/>
-    <col width="12" customWidth="1" style="25" min="4" max="4"/>
-    <col width="8" bestFit="1" customWidth="1" style="25" min="6" max="6"/>
+    <col width="12" customWidth="1" style="26" min="1" max="1"/>
+    <col width="27.83203125" customWidth="1" style="26" min="2" max="2"/>
+    <col width="72.5" bestFit="1" customWidth="1" style="26" min="3" max="3"/>
+    <col width="12" customWidth="1" style="26" min="4" max="4"/>
+    <col width="8" bestFit="1" customWidth="1" style="26" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="25">
+    <row r="1" ht="18" customHeight="1" s="26">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>분석번호</t>
@@ -1549,13 +2339,13 @@
           <t>분석대상</t>
         </is>
       </c>
-      <c r="F1" s="33" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>기준월</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="25">
+    <row r="2" ht="16" customHeight="1" s="26">
       <c r="A2" s="6" t="n">
         <v>2</v>
       </c>
@@ -1571,7 +2361,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1579,8 +2369,11 @@
           <t>전체</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="25">
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="26">
       <c r="A3" s="7" t="n">
         <v>3</v>
       </c>
@@ -1596,7 +2389,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1605,7 +2398,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="25">
+    <row r="4" ht="16" customHeight="1" s="26">
       <c r="A4" s="6" t="n">
         <v>4</v>
       </c>
@@ -1630,7 +2423,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="25">
+    <row r="5" ht="16" customHeight="1" s="26">
       <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
@@ -1646,7 +2439,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1655,7 +2448,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="25">
+    <row r="6" ht="16" customHeight="1" s="26">
       <c r="A6" s="6" t="n">
         <v>6</v>
       </c>
@@ -1680,7 +2473,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="25">
+    <row r="7" ht="16" customHeight="1" s="26">
       <c r="A7" s="7" t="n">
         <v>7</v>
       </c>
@@ -1721,7 +2514,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1771,7 +2564,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1796,12 +2589,12 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>당기</t>
         </is>
       </c>
     </row>
@@ -1846,7 +2639,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1871,7 +2664,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1891,12 +2684,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>계정별 월별 추이 및 샘플 추출 → AI계정별분석 시트 참조</t>
+          <t>계정별 월별 추이 및 샘플 추출 → 26번 메뉴와 관계없으나 26번 메뉴의 백데이터성격이므로 26번과 같이 실행하면 좋음</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1921,7 +2714,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1946,7 +2739,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1996,7 +2789,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2021,7 +2814,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2046,7 +2839,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2071,7 +2864,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2096,7 +2889,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2116,7 +2909,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2126,12 +2919,12 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="8" t="n">
         <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>손익월별분析</t>
+          <t>손익월별분석</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2149,6 +2942,61 @@
           <t>전체</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AI계정별분석_실행</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>계정별 월별 추이 및 샘플을 Gemini로 분석실행(15번 메뉴와 관계없이 독립적으로 실행)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" s="26"/>
+    <row r="28" s="26">
+      <c r="A28" s="28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>감가상각_평가손익분석</t>
+        </is>
+      </c>
+      <c r="C28" s="28" t="inlineStr">
+        <is>
+          <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
+        </is>
+      </c>
+      <c r="D28" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="n"/>
     </row>
     <row r="30">
       <c r="B30" t="inlineStr">
@@ -2189,11 +3037,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2201,60 +3046,21 @@
           <t>계정과목</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미수대매금(국제항공권판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>항공권판매(국제)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>외상매출금(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>미수금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>미수금(기 타)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>용역매출액(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>미지급금(일반)</t>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2269,645 +3075,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="26.1640625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>실행여부</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>자산</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>미수금환불(국제항공)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>정기예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>수탁금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>외상매출금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>투자매도가능증권</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>미수금(카드판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>선급금(입체금-해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>상품(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>미수금(호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>미수금(국제항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>상품(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>수탁금(호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>선급금(입체금-호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>선급금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>정기성예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>선급금(일반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>장기대여금</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>미수금(국제항공권-정산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>미수수익</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>외화예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>가수금</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>항공권판매(국제)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>예수금(국제항공권환불)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>미지급금(국제항공권-정산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>미지급금(일반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>선수금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>외상매입금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>미지급금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>외상매입금(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>미지급금(호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>미지급금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>예수금(결산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>미지급금(회사카드사용분-단체)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>예수금(갑근세)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>용역매출액(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>항공권판매(국제항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>매출액(국제항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>상품매출액(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>매출액(기타항공권판매수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>매출액(해외여행알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>매출액(해외호텔알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>용역매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>매출액(국내관광알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>매출액(국제항공권판매수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>매출액(여권비자취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>매출액(국내호텔콘도알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>매출액(기타)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>매출액(국내항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>매출액(국내항공권판매수입)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2922,34 +3113,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="27.33203125" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="26">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2958,20 +3144,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>매출액(국내호텔콘도알선수입)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2980,20 +3161,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미수대매금(국제항공권판매)</t>
+          <t>매출액(국제항공권판매수입)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3002,20 +3178,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>항공권판매(국제)</t>
+          <t>매출액(국제항공취급수수료)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3024,20 +3195,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>외상매출금(PLM)</t>
+          <t>매출액(해외여행알선수입)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3046,20 +3212,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>미수금(해외여행알선)</t>
+          <t>상품매출액(PLM)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3068,20 +3229,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>미수금(기 타)</t>
+          <t>상품매출액(S&amp;C)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>차변</t>
+          <t>대변</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3090,7 +3246,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>상품매출액(PLM)</t>
+          <t>상품매출액(정보기술)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3099,11 +3255,6 @@
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3112,7 +3263,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>용역매출액(S&amp;C)</t>
+          <t>용역매출액(PLM)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3121,11 +3272,6 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3134,7 +3280,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>미지급금(일반)</t>
+          <t>용역매출액(S&amp;C)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3144,10 +3290,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>용역매출액(정보기술)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3164,175 +3322,72 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
-    <col width="10" customWidth="1" style="25" min="2" max="2"/>
-    <col width="12" customWidth="1" style="25" min="3" max="3"/>
-    <col width="42" customWidth="1" style="25" min="4" max="4"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="25">
-      <c r="A2" s="2" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="25">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>외상매출금(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="25">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>미수금(해외여행알선)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>항공권판매(국제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>외상매출금(PLM)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>미수금(국제항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="25">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="25">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>예수금(국제항공권환불)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
+          <t>미수금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미수금(기 타)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매입금(상품)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>선급금(입체금-국내관광알선)</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>상품매출액(PLM)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>선수금(국제항공권)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>용역매출액(PLM)</t>
         </is>
       </c>
     </row>
@@ -3342,36 +3397,16 @@
           <t>용역매출액(S&amp;C)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>매출액(국제항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미지급금(일반)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3381,108 +3416,650 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" style="25" min="1" max="1"/>
-    <col width="10" customWidth="1" style="25" min="2" max="2"/>
-    <col width="16.6640625" customWidth="1" style="25" min="3" max="3"/>
-    <col width="12" customWidth="1" style="25" min="4" max="4"/>
-    <col width="36" customWidth="1" style="25" min="5" max="5"/>
+    <col width="26.1640625" bestFit="1" customWidth="1" style="26" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="25">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>최소금액</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="25">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="27" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="25">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" s="28" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="25">
-      <c r="A4" s="2" t="inlineStr">
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="27" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>미수금환불(국제항공)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>정기예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>수탁금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>외상매출금(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>투자매도가능증권</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>미수금(카드판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>선급금(입체금-해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>상품(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>미수금(호텔콘도판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>미수금(국제항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>상품(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>수탁금(호텔콘도판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>선급금(입체금-호텔콘도판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>선급금(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>정기성예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>선급금(일반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>장기대여금</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>미수금(국제항공권-정산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>미수수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>가수금</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>항공권판매(국제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>예수금(국제항공권환불)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>미지급금(국제항공권-정산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>미지급금(일반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>선수금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>외상매입금(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>미지급금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>외상매입금(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>미지급금(호텔콘도판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>미지급금(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>예수금(결산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>미지급금(회사카드사용분-단체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>예수금(갑근세)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>항공권판매(국제항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>매출액(국제항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>매출액(기타항공권판매수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>매출액(해외여행알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>매출액(해외호텔알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>용역매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>매출액(국내관광알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>매출액(국제항공권판매수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>매출액(여권비자취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>매출액(국내호텔콘도알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>매출액(기타)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>매출액(국내항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>매출액(국내항공권판매수입)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3492,117 +4069,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="25" min="2" max="2"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>용역매출액(S&amp;C)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>상품매출액(PLM)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>항공권판매(국제)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>매출액(국제항공취급수수료)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>외상매출금(PLM)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>상품매출액(S&amp;C)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>미수금(해외여행알선)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>매출액(기타항공권판매수입)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>미수금(기 타)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>지급수수료(S&amp;C)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>상품매출액(PLM)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>지급수수료(PLM)</t>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>용역매출액(S&amp;C)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>접대비</t>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>미지급금(일반)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3617,397 +4311,213 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="30.58203125" bestFit="1" customWidth="1" style="25" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="10" customWidth="1" style="26" min="2" max="2"/>
+    <col width="12" customWidth="1" style="26" min="3" max="3"/>
+    <col width="42" customWidth="1" style="26" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정영</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>외상매출금(국제항공권판매수수료)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>외상매출금(국내항공권판매수수료)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>외상매출금(상품)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
+    <row r="1" ht="18" customHeight="1" s="26">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="26">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="26">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>외상매출금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="26">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>미수금(해외여행알선)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>선급금(보험가입대급금)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>선급금(에스앤씨)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>선급금(여권및비자대)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
+          <t>미수금(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="26">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" s="26">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>예수금(국제항공권환불)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>선급금(일반)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>차변</t>
+          <t>선급금(입체금-국내관광알선)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>선급금(입체금-국내관광알선)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>차변</t>
+          <t>선수금(국제항공권)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>선급금(입체금-해외여행알선)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>차변</t>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>미수금(국내관광알선)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>미수금(국내항공권-정산)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>미수금(국내항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>미수금(국제항공권-정산)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>미수금(국제항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>미수금(기타)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>미수금(에스앤씨)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>미수금(여권비자취급수수료)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>미수금(정보기술)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>미수금(카드판매)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>미수금(해외여행알선)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>미수금(해외여행환불)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>미수금(호텔콘도판매)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>미수대매금(국내항공권판매)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매 ADM)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>단기대여금</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>장기대여금</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>매출액(기타항공권판매수입)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
+          <t>매출액(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>매출액(국제항공권취급수수료)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>매출액해외여행알선수입</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>매출액상품</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>대변</t>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -23,6 +23,7 @@
     <sheet name="거래처 분석" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="감가상각_평가손익분석" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2297,6 +2298,175 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="26" min="1" max="1"/>
+    <col width="26" customWidth="1" style="26" min="2" max="2"/>
+    <col width="10" customWidth="1" style="26" min="3" max="3"/>
+    <col width="55" customWidth="1" style="26" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>유형자산계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>감가상각누계액계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>건물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>구축물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기계장치감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차량운반구감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>비품</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>비품감가상각누계액</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -2304,7 +2304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="26" min="1" max="1"/>
@@ -2326,10 +2326,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>대체상대계정</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>취득원가_수동조정</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상각누계액_수동조정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2341,12 +2356,12 @@
           <t>토지</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
         </is>
@@ -2363,12 +2378,12 @@
           <t>건물감가상각누계액</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
         </is>
@@ -2385,12 +2400,12 @@
           <t>구축물감가상각누계액</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
         </is>
@@ -2407,12 +2422,12 @@
           <t>기계장치감가상각누계액</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
         </is>
@@ -2429,12 +2444,12 @@
           <t>차량운반구감가상각누계액</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
         </is>
@@ -2451,12 +2466,12 @@
           <t>비품감가상각누계액</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
         </is>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -3183,6 +3183,7 @@
       </c>
       <c r="F28" s="28" t="n"/>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
@@ -3204,6 +3205,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="1" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="감가상각_평가손익분석" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="감가상각_유형자산롤포워드" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="유형자산_처분손익" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -35,7 +36,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -108,13 +109,6 @@
       <charset val="129"/>
       <family val="3"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <charset val="129"/>
-      <family val="2"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -239,7 +233,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -313,6 +307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -320,7 +315,9 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -695,14 +692,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" style="26" min="1" max="1"/>
-    <col width="22" customWidth="1" style="26" min="2" max="2"/>
-    <col width="30" customWidth="1" style="26" min="3" max="3"/>
+    <col width="18" customWidth="1" style="27" min="1" max="1"/>
+    <col width="22" customWidth="1" style="27" min="2" max="2"/>
+    <col width="30" customWidth="1" style="27" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="26">
+    <row r="1" ht="18" customHeight="1" s="27">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
@@ -719,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="26">
+    <row r="2" ht="16" customHeight="1" s="27">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ClientName</t>
@@ -732,7 +729,7 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="26">
+    <row r="3" ht="16" customHeight="1" s="27">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>StartDate</t>
@@ -747,7 +744,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="26">
+    <row r="4" ht="16" customHeight="1" s="27">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EndDate</t>
@@ -758,7 +755,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1" s="26">
+    <row r="5" ht="16" customHeight="1" s="27">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TargetYear</t>
@@ -781,16 +778,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="16" customWidth="1" style="26" min="1" max="1"/>
-    <col width="10" customWidth="1" style="26" min="2" max="2"/>
-    <col width="16.6640625" customWidth="1" style="26" min="3" max="3"/>
-    <col width="12" customWidth="1" style="26" min="4" max="4"/>
-    <col width="36" customWidth="1" style="26" min="5" max="5"/>
+    <col width="16" customWidth="1" style="27" min="1" max="1"/>
+    <col width="10" customWidth="1" style="27" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" style="27" min="3" max="3"/>
+    <col width="12" customWidth="1" style="27" min="4" max="4"/>
+    <col width="36" customWidth="1" style="27" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="26">
+    <row r="1" ht="18" customHeight="1" s="27">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -817,7 +814,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="26">
+    <row r="2" ht="16" customHeight="1" s="27">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -828,7 +825,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C2" s="29" t="n">
+      <c r="C2" s="30" t="n">
         <v>1000000000</v>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -838,7 +835,7 @@
       </c>
       <c r="E2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="26">
+    <row r="3" ht="16" customHeight="1" s="27">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>(전체)</t>
@@ -849,7 +846,7 @@
           <t>대변</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C3" s="31" t="n">
         <v>1000000000</v>
       </c>
       <c r="D3" s="7" t="inlineStr">
@@ -859,7 +856,7 @@
       </c>
       <c r="E3" s="3" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1" s="26">
+    <row r="4" ht="16" customHeight="1" s="27">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>보통예금</t>
@@ -870,7 +867,7 @@
           <t>차변</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>500000000</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -892,9 +889,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="2" max="2"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1017,9 +1014,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="41.9140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="41.9140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1442,9 +1439,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="23.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="23.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1630,9 +1627,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="20.25" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="20.25" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1788,22 +1785,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" style="26" min="1" max="1"/>
-    <col width="25" customWidth="1" style="26" min="2" max="2"/>
-    <col width="35" customWidth="1" style="26" min="3" max="3"/>
-    <col width="10" customWidth="1" style="26" min="4" max="5"/>
+    <col width="18" customWidth="1" style="27" min="1" max="1"/>
+    <col width="25" customWidth="1" style="27" min="2" max="2"/>
+    <col width="35" customWidth="1" style="27" min="3" max="3"/>
+    <col width="10" customWidth="1" style="27" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="26">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="27">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="26">
+    <row r="2" ht="20" customHeight="1" s="27">
       <c r="A2" s="15" t="inlineStr">
         <is>
           <t>작업명</t>
@@ -1830,7 +1827,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="26">
+    <row r="3" ht="18" customHeight="1" s="27">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>분석01</t>
@@ -1857,7 +1854,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="26">
+    <row r="4" ht="18" customHeight="1" s="27">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>분석02</t>
@@ -1884,7 +1881,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="26">
+    <row r="5" ht="18" customHeight="1" s="27">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>분석03</t>
@@ -1911,7 +1908,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="26">
+    <row r="6" ht="18" customHeight="1" s="27">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>분석04</t>
@@ -1934,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="26">
+    <row r="7" ht="18" customHeight="1" s="27">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>분석05</t>
@@ -1953,35 +1950,35 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="26">
+    <row r="8" ht="18" customHeight="1" s="27">
       <c r="A8" s="16" t="n"/>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="16" t="n"/>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="26">
+    <row r="9" ht="18" customHeight="1" s="27">
       <c r="A9" s="16" t="n"/>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="16" t="n"/>
       <c r="D9" s="17" t="n"/>
       <c r="E9" s="17" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="26">
+    <row r="10" ht="18" customHeight="1" s="27">
       <c r="A10" s="16" t="n"/>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="16" t="n"/>
       <c r="D10" s="17" t="n"/>
       <c r="E10" s="17" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="26">
+    <row r="11" ht="18" customHeight="1" s="27">
       <c r="A11" s="16" t="n"/>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="16" t="n"/>
       <c r="D11" s="17" t="n"/>
       <c r="E11" s="17" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="26">
+    <row r="12" ht="18" customHeight="1" s="27">
       <c r="A12" s="16" t="n"/>
       <c r="B12" s="16" t="n"/>
       <c r="C12" s="16" t="n"/>
@@ -2004,20 +2001,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="25" customWidth="1" style="26" min="1" max="1"/>
-    <col width="10" customWidth="1" style="26" min="2" max="3"/>
+    <col width="25" customWidth="1" style="27" min="1" max="1"/>
+    <col width="10" customWidth="1" style="27" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="26">
-      <c r="A1" s="27" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="27">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리 | 거래처별 비교는 2번 메뉴 사용</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="26">
+    <row r="2" ht="20" customHeight="1" s="27">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -2034,7 +2031,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="26">
+    <row r="3" ht="18" customHeight="1" s="27">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>상품매출액(PLM)</t>
@@ -2051,7 +2048,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="26">
+    <row r="4" ht="18" customHeight="1" s="27">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>상품매출액(PLM)</t>
@@ -2068,7 +2065,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="26">
+    <row r="5" ht="18" customHeight="1" s="27">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>상품매출액(PLM)</t>
@@ -2085,7 +2082,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="26">
+    <row r="6" ht="18" customHeight="1" s="27">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>상품매출액(S&amp;C)</t>
@@ -2102,32 +2099,32 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="26">
+    <row r="7" ht="18" customHeight="1" s="27">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="20" t="n"/>
       <c r="C7" s="20" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="26">
+    <row r="8" ht="18" customHeight="1" s="27">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="20" t="n"/>
       <c r="C8" s="20" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="26">
+    <row r="9" ht="18" customHeight="1" s="27">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="20" t="n"/>
       <c r="C9" s="20" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="26">
+    <row r="10" ht="18" customHeight="1" s="27">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="20" t="n"/>
       <c r="C10" s="20" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="26">
+    <row r="11" ht="18" customHeight="1" s="27">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="20" t="n"/>
       <c r="C11" s="20" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="26">
+    <row r="12" ht="18" customHeight="1" s="27">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="20" t="n"/>
       <c r="C12" s="20" t="n"/>
@@ -2147,13 +2144,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="30" customWidth="1" style="26" min="1" max="1"/>
-    <col width="10" customWidth="1" style="26" min="2" max="2"/>
-    <col width="12" customWidth="1" style="26" min="3" max="3"/>
-    <col width="10" customWidth="1" style="26" min="4" max="4"/>
-    <col width="55" customWidth="1" style="26" min="5" max="5"/>
+    <col width="36.75" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="10" customWidth="1" style="27" min="2" max="2"/>
+    <col width="12" customWidth="1" style="27" min="3" max="3"/>
+    <col width="10" customWidth="1" style="27" min="4" max="4"/>
+    <col width="55" customWidth="1" style="27" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2304,13 +2301,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="22" customWidth="1" style="26" min="1" max="1"/>
-    <col width="26" customWidth="1" style="26" min="2" max="2"/>
-    <col width="10" customWidth="1" style="26" min="3" max="3"/>
-    <col width="55" customWidth="1" style="26" min="4" max="4"/>
+    <col width="22" customWidth="1" style="27" min="1" max="1"/>
+    <col width="26" customWidth="1" style="27" min="2" max="2"/>
+    <col width="10" customWidth="1" style="27" min="3" max="3"/>
+    <col width="55" customWidth="1" style="27" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2363,7 +2360,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+          <t>토지는 감가상각 대상 아님(감가상각누계액 계정 없음). 취득원가 계정명도 당기/전기 이동 없어 분개장에 미노출 — 사용자 확인 예정 (2026-08-12)</t>
         </is>
       </c>
     </row>
@@ -2380,68 +2377,68 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+          <t>감가상각누계액 계정명은 확인됨. 취득원가 계정명은 당기/전기 모두 취득·처분 이동이 없어 분개장에 노출되지 않음 — 사용자가 계정과목표 확인 후 별도 회신 예정 (2026-08-12) | 원가계정명 미확인 상태로 켜두면 감가상각누계액 계정이 접두어 일치로 오매칭되어 실행여부 N으로 꺼둠 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>구축물</t>
+          <t>건물(투자)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>구축물감가상각누계액</t>
+          <t>건물(투자)감가상각누계액</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+          <t>감가상각누계액 계정명은 확인됨. 취득원가 계정명은 당기/전기 모두 취득·처분 이동이 없어 분개장에 노출되지 않음 — 사용자가 계정과목표 확인 후 별도 회신 예정 (2026-08-12) | 원가계정명 미확인 상태로 켜두면 감가상각누계액 계정이 접두어 일치로 오매칭되어 실행여부 N으로 꺼둠 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>기계장치</t>
+          <t>구축물</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>기계장치감가상각누계액</t>
+          <t>구축물감가상각누계액</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+          <t>감가상각누계액 계정명은 확인됨. 취득원가 계정명은 당기/전기 모두 취득·처분 이동이 없어 분개장에 노출되지 않음 — 사용자가 계정과목표 확인 후 별도 회신 예정 (2026-08-12) | 원가계정명 미확인 상태로 켜두면 감가상각누계액 계정이 접두어 일치로 오매칭되어 실행여부 N으로 꺼둠 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>차량운반구</t>
+          <t>기계장치</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>차량운반구감가상각누계액</t>
+          <t>기계장치감가상각누계액</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2451,19 +2448,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비품</t>
+          <t>기구비품</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>비품감가상각누계액</t>
+          <t>기구비품감가상각누계액</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2473,7 +2470,109 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>예시 계정명 — sejoong 실제 계정과목명으로 확인/수정 필요</t>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차량감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료 (기존 예시의 차량운반구감가상각누계액 -&gt; 차량감가상각누계액으로 정정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>사용권자산감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료 (신규 추가)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>처분이익계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>처분손실계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>영업외수익(유형자산처분이익)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>영업외비용(유형자산처분손실)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>실제 sejoong 계정과목명 확인됨 (2026-08-12). 단 감가상각_유형자산롤포워드 시트 계정명이 아직 예시 상태라 그것부터 확정 후 Y로 전환할 것</t>
         </is>
       </c>
     </row>
@@ -2488,17 +2587,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" style="26" min="1" max="1"/>
-    <col width="27.83203125" customWidth="1" style="26" min="2" max="2"/>
-    <col width="72.5" bestFit="1" customWidth="1" style="26" min="3" max="3"/>
-    <col width="12" customWidth="1" style="26" min="4" max="4"/>
-    <col width="8" bestFit="1" customWidth="1" style="26" min="6" max="6"/>
+    <col width="12" customWidth="1" style="27" min="1" max="1"/>
+    <col width="27.83203125" customWidth="1" style="27" min="2" max="2"/>
+    <col width="72.5" bestFit="1" customWidth="1" style="27" min="3" max="3"/>
+    <col width="12" customWidth="1" style="27" min="4" max="4"/>
+    <col width="8" bestFit="1" customWidth="1" style="27" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="26">
+    <row r="1" ht="18" customHeight="1" s="27">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>분석번호</t>
@@ -2530,7 +2629,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="26">
+    <row r="2" ht="16" customHeight="1" s="27">
       <c r="A2" s="6" t="n">
         <v>2</v>
       </c>
@@ -2558,7 +2657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="26">
+    <row r="3" ht="16" customHeight="1" s="27">
       <c r="A3" s="7" t="n">
         <v>3</v>
       </c>
@@ -2583,7 +2682,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="26">
+    <row r="4" ht="16" customHeight="1" s="27">
       <c r="A4" s="6" t="n">
         <v>4</v>
       </c>
@@ -2608,7 +2707,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="26">
+    <row r="5" ht="16" customHeight="1" s="27">
       <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
@@ -2633,7 +2732,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="26">
+    <row r="6" ht="16" customHeight="1" s="27">
       <c r="A6" s="6" t="n">
         <v>6</v>
       </c>
@@ -2658,7 +2757,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="26">
+    <row r="7" ht="16" customHeight="1" s="27">
       <c r="A7" s="7" t="n">
         <v>7</v>
       </c>
@@ -3156,58 +3255,57 @@
         </is>
       </c>
     </row>
-    <row r="27" s="26"/>
-    <row r="28" s="26">
-      <c r="A28" s="28" t="n">
+    <row r="27">
+      <c r="A27" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="28" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>감가상각_평가손익분석</t>
         </is>
       </c>
-      <c r="C28" s="28" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D27" s="25" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>당기</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
-    </row>
-    <row r="29"/>
+      <c r="F27" s="25" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>별도분석시트 필요없는 분석</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>별도분석시트 필요없는 분석</t>
+          <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있어도 분석실행 안 됨</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>본 분석목록시트에 실행여부가 N이면 관련분석시트가 있어도 분석실행 안 됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
           <t>분 분석목록시트에 실행여부가 Y이고 관련분서시트가 없으면 기본분석값으로 실행</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="C34" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="C33" t="inlineStr">
         <is>
           <t>4,5,6,16,19,22</t>
         </is>
@@ -3301,12 +3399,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="27.33203125" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="27.33203125" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="26">
+    <row r="1" ht="18" customHeight="1" s="27">
       <c r="A1" s="22" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -3510,9 +3608,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3604,9 +3702,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="26.1640625" bestFit="1" customWidth="1" style="26" min="2" max="2"/>
+    <col width="26.1640625" bestFit="1" customWidth="1" style="27" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4257,9 +4355,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4499,15 +4597,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="26" min="1" max="1"/>
-    <col width="10" customWidth="1" style="26" min="2" max="2"/>
-    <col width="12" customWidth="1" style="26" min="3" max="3"/>
-    <col width="42" customWidth="1" style="26" min="4" max="4"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="10" customWidth="1" style="27" min="2" max="2"/>
+    <col width="12" customWidth="1" style="27" min="3" max="3"/>
+    <col width="42" customWidth="1" style="27" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="26">
+    <row r="1" ht="18" customHeight="1" s="27">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -4529,7 +4627,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="26">
+    <row r="2" ht="16" customHeight="1" s="27">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>미수대매금(국제항공권판매)</t>
@@ -4547,7 +4645,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="26">
+    <row r="3" ht="16" customHeight="1" s="27">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>외상매출금(S&amp;C)</t>
@@ -4565,7 +4663,7 @@
       </c>
       <c r="D3" s="3" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1" s="26">
+    <row r="4" ht="16" customHeight="1" s="27">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>미수금(해외여행알선)</t>
@@ -4600,7 +4698,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="26">
+    <row r="6" ht="16" customHeight="1" s="27">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>보통예금</t>
@@ -4618,7 +4716,7 @@
       </c>
       <c r="D6" s="13" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1" s="26">
+    <row r="7" ht="16" customHeight="1" s="27">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>예수금(국제항공권환불)</t>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -692,7 +692,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="18" customWidth="1" style="27" min="1" max="1"/>
     <col width="22" customWidth="1" style="27" min="2" max="2"/>
@@ -778,7 +778,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" style="27" min="1" max="1"/>
     <col width="10" customWidth="1" style="27" min="2" max="2"/>
@@ -889,7 +889,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="2" max="2"/>
   </cols>
@@ -1014,7 +1014,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="41.9140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
@@ -1439,7 +1439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="23.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
@@ -1627,7 +1627,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="20.25" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
@@ -1785,7 +1785,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="18" customWidth="1" style="27" min="1" max="1"/>
     <col width="25" customWidth="1" style="27" min="2" max="2"/>
@@ -2001,7 +2001,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25" customWidth="1" style="27" min="1" max="1"/>
     <col width="10" customWidth="1" style="27" min="2" max="3"/>
@@ -2144,7 +2144,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="36.75" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
     <col width="10" customWidth="1" style="27" min="2" max="2"/>
@@ -2302,7 +2302,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="22" customWidth="1" style="27" min="1" max="1"/>
     <col width="26" customWidth="1" style="27" min="2" max="2"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>감가상각누계액 계정명은 확인됨. 취득원가 계정명은 당기/전기 모두 취득·처분 이동이 없어 분개장에 노출되지 않음 — 사용자가 계정과목표 확인 후 별도 회신 예정 (2026-08-12) | 원가계정명 미확인 상태로 켜두면 감가상각누계액 계정이 접두어 일치로 오매칭되어 실행여부 N으로 꺼둠 (2026-08-12)</t>
+          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>감가상각누계액 계정명은 확인됨. 취득원가 계정명은 당기/전기 모두 취득·처분 이동이 없어 분개장에 노출되지 않음 — 사용자가 계정과목표 확인 후 별도 회신 예정 (2026-08-12) | 원가계정명 미확인 상태로 켜두면 감가상각누계액 계정이 접두어 일치로 오매칭되어 실행여부 N으로 꺼둠 (2026-08-12)</t>
+          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>감가상각누계액 계정명은 확인됨. 취득원가 계정명은 당기/전기 모두 취득·처분 이동이 없어 분개장에 노출되지 않음 — 사용자가 계정과목표 확인 후 별도 회신 예정 (2026-08-12) | 원가계정명 미확인 상태로 켜두면 감가상각누계액 계정이 접두어 일치로 오매칭되어 실행여부 N으로 꺼둠 (2026-08-12)</t>
+          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
     <col width="27.83203125" customWidth="1" style="27" min="2" max="2"/>
@@ -3281,7 +3281,6 @@
       </c>
       <c r="F27" s="25" t="n"/>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
@@ -3303,7 +3302,6 @@
         </is>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
@@ -3399,7 +3397,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="27.33203125" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
@@ -3608,7 +3606,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
@@ -3702,7 +3700,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B53"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="26.1640625" bestFit="1" customWidth="1" style="27" min="2" max="2"/>
   </cols>
@@ -4355,7 +4353,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
   </cols>
@@ -4597,7 +4595,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
     <col width="10" customWidth="1" style="27" min="2" max="2"/>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -2000,7 +2000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="25" customWidth="1" style="27" min="1" max="1"/>
@@ -2030,6 +2030,11 @@
           <t>실행여부</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>손익구분</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="27">
       <c r="A3" s="16" t="inlineStr">
@@ -2047,6 +2052,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="27">
       <c r="A4" s="16" t="inlineStr">
@@ -2064,6 +2074,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="27">
       <c r="A5" s="16" t="inlineStr">
@@ -2081,6 +2096,11 @@
           <t>Y</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="27">
       <c r="A6" s="16" t="inlineStr">
@@ -2096,6 +2116,11 @@
       <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>매출</t>
         </is>
       </c>
     </row>

--- a/journal_analyzer/sejoong/task_list_sejoong.xlsx
+++ b/journal_analyzer/sejoong/task_list_sejoong.xlsx
@@ -3,28 +3,29 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-19298" yWindow="-98" windowWidth="19396" windowHeight="12196" tabRatio="600" firstSheet="6" activeTab="9" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="분석목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="AI 계정별 분석" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="AI계정별분석_실행" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="거래처 전기_당기 비교" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="심층분석 (계정별 Top) " sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="총계정원장" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="상대계정 분석" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="벤포드 분석" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="라운드넘버 분석" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="매출 vs 비용 교차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="잔액증감분석 (게정별 거래처벌)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="특수관계자 분석" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="은행조회서 완전성" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="거래처 분석" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="감가상각_평가손익분석" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="감가상각_유형자산롤포워드" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="유형자산_처분손익" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="02_거래처 전기_당기 비교" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_벤포드 분석" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="08_상대계정 분석" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="10_라운드넘버 분석" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="11_특수관계자 분석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="12_자산 vs 부채 교차" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="13_매출 vs 비용 교차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="14_심층분석 (계정별 Top) " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="15_AI 계정별 분석" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="17_거래처 분석" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="20_잔액증감분석 (계정별 거래처별)" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="21_총계정원장" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="22_은행조회서 완전성" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="25_손익월별분석" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="26_AI계정별분석_실행" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="27_감가상각_평가손익분석" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="감가상각_유형자산롤포워드" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="유형자산_처분손익" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -308,15 +309,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
@@ -694,12 +695,12 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="27" min="1" max="1"/>
-    <col width="22" customWidth="1" style="27" min="2" max="2"/>
-    <col width="30" customWidth="1" style="27" min="3" max="3"/>
+    <col width="18" customWidth="1" style="28" min="1" max="1"/>
+    <col width="22" customWidth="1" style="28" min="2" max="2"/>
+    <col width="30" customWidth="1" style="28" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="27">
+    <row r="1" ht="18" customHeight="1" s="28">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>항목</t>
@@ -716,7 +717,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="27">
+    <row r="2" ht="16" customHeight="1" s="28">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>ClientName</t>
@@ -729,7 +730,7 @@
       </c>
       <c r="C2" s="2" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="27">
+    <row r="3" ht="16" customHeight="1" s="28">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>StartDate</t>
@@ -744,7 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="27">
+    <row r="4" ht="16" customHeight="1" s="28">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>EndDate</t>
@@ -755,7 +756,7 @@
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1" s="27">
+    <row r="5" ht="16" customHeight="1" s="28">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>TargetYear</t>
@@ -777,108 +778,91 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="16" customWidth="1" style="27" min="1" max="1"/>
-    <col width="10" customWidth="1" style="27" min="2" max="2"/>
-    <col width="16.6640625" customWidth="1" style="27" min="3" max="3"/>
-    <col width="12" customWidth="1" style="27" min="4" max="4"/>
-    <col width="36" customWidth="1" style="27" min="5" max="5"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="27">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>최소금액</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="27">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="30" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="27">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>(전체)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C3" s="31" t="n">
-        <v>1000000000</v>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="27">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="n">
-        <v>500000000</v>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>항공권판매(국제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>외상매출금(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>미수금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>미수금(기 타)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상매입금(상품)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>용역매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>미지급금(일반)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -888,117 +872,105 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="2" max="2"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>실행여부</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>용역매출액(S&amp;C)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>외상매출금(상품)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>상품매출액(PLM)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>미수금(기타)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>매출액(국제항공취급수수료)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>상품매출액(S&amp;C)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>매출</t>
+          <t>매출액(국제항공권취급수수료)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>매출액(기타항공권판매수입)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>매출액상품</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>지급수수료(S&amp;C)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비용</t>
+          <t>매출액용역</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>지급수수료(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>비용</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>접대비</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1010,425 +982,216 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="41.9140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="18" customWidth="1" style="28" min="1" max="1"/>
+    <col width="25" customWidth="1" style="28" min="2" max="2"/>
+    <col width="35" customWidth="1" style="28" min="3" max="3"/>
+    <col width="10" customWidth="1" style="28" min="4" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>계정영</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>외상매출금(항공권판매-국내항공권판매수수료)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>외상매출금(항공권판매-국제항공권판매수수료)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>외상매출금(상품)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>외상매출금(PLM)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>외상매출금(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>외상매출금(정보기술)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>선급금(보험가입대급금)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>선급금(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>선급금(여권및비자대)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>선급금(일반)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>선급금(입체금-국내관광알선)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>선급금(입체금-해외여행알선)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>미수금(국내관광알선)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>미수금(국내항공권-정산)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>미수금(국내항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>미수금(국제항공권-정산)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>미수금(국제항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>미수금(기타)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>미수금(에스앤씨)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>미수금(여권비자취급수수료)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>미수금(정보기술)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>미수금(카드판매)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>미수금(해외여행알선)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>미수금(해외여행환불)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>미수금(호텔콘도판매)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>미수대매금(국내항공권판매)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매 ADM)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>단기대여금</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>장기대여금</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>외상매입금(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="28">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="28">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>작업명</t>
+        </is>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>계정과목</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="28">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>분석01</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>삼성전자(주)</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>외상매입금(PLM)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="28">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>분석02</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>링커코리아 주식회사</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>외상매입금(정보기술)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="28">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>분석03</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>현대오토에버 주식회사</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>대변</t>
         </is>
       </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="28">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>분석04</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="28">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>분석05</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="28">
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="28">
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="28">
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="28">
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="28">
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1438,185 +1201,422 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="23.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="41.9140625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>거래처명</t>
+          <t>계정영</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>실행여부</t>
+          <t>구분</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(주)세중샤론손해보험중개</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(항공권판매-국내항공권판매수수료)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대표이사</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(항공권판매-국제항공권판매수수료)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>세중엔지니어링</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(상품)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>(주)세중엔지니어링</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(PLM)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>(재)우리옛돌문화재단</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>㈜세중인터내셔널</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(정보기술)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>(주)세성항운</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선급금(보험가입대급금)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(주)세중로지스틱스</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선급금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>세중인터내셔널</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선급금(여권및비자대)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>천신일</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선급금(일반)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>천세전</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선급금(입체금-국내관광알선)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>천호전</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선급금(입체금-해외여행알선)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>천미전</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미수금(국내관광알선)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>차변</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="n"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>미수금(국내항공권-정산)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>미수금(국내항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>미수금(국제항공권-정산)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>미수금(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>미수금(기타)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>미수금(에스앤씨)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>미수금(여권비자취급수수료)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>미수금(정보기술)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>미수금(카드판매)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>미수금(해외여행알선)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>미수금(해외여행환불)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>미수금(호텔콘도판매)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>미수대매금(국내항공권판매)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매 ADM)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>단기대여금</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>장기대여금</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>외상매입금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>외상매입금(PLM)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>외상매입금(정보기술)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1626,15 +1626,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="20.25" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="26.1640625" bestFit="1" customWidth="1" style="28" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>계정과목</t>
         </is>
       </c>
@@ -1642,353 +1647,771 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>단기차입금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>장기차입금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>미수금환불(국제항공)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>유동성장기부채</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>정기예금</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>유동성장기차입금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>수탁금(해외여행알선)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전환사채</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>외상매출금(S&amp;C)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>유동성전환사채</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>투자매도가능증권</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>전환상환우선주</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>미수금(카드판매)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>유동성전환상환우선주</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>선급금(입체금-해외여행알선)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>상품(PLM)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>외화예금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>미수금(호텔콘도판매)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>외화정기예금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>미수금(국제항공취급수수료)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>정기성예금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>상품(S&amp;C)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>정기예금</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>수탁금(호텔콘도판매)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>보험료(보증보험)</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>선급금(입체금-호텔콘도판매)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>보험료(세중)</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>선급금(S&amp;C)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>보험료(세중S&amp;C)</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>정기성예금</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>보험료(자동차보험)</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>선급금(일반)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>보험료-기타</t>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>장기대여금</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>미수금(국제항공권-정산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>미수수익</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>자산</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>가수금</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>항공권판매(국제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>예수금(국제항공권환불)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>미지급금(국제항공권-정산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>미지급금(일반)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>선수금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>외상매입금(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>미지급금(해외여행알선)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>외상매입금(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>미지급금(호텔콘도판매)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>미지급금(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>예수금(결산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>미지급금(회사카드사용분-단체)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>부채</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>예수금(갑근세)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>항공권판매(국제항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>매출액(국제항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>매출액(기타항공권판매수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>매출액(해외여행알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>매출액(해외호텔알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>용역매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>매출액(국내관광알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>매출액(국제항공권판매수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>매출액(여권비자취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>매출액(국내호텔콘도알선수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>매출액(기타)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>매출액(국내항공취급수수료)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>매출액(국내항공권판매수입)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="18" customWidth="1" style="27" min="1" max="1"/>
-    <col width="25" customWidth="1" style="27" min="2" max="2"/>
-    <col width="35" customWidth="1" style="27" min="3" max="3"/>
-    <col width="10" customWidth="1" style="27" min="4" max="5"/>
+    <col width="20.25" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="27">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>※ 사용법: 작업명(자유기재) / 계정과목·거래처명은 콤마로 여러 개 가능 / 금액열: 차변·대변·both / 실행여부 Y인 행만 처리됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="27">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>작업명</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
-        <is>
-          <t>거래처명</t>
-        </is>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="27">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>분석01</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>삼성전자(주)</t>
-        </is>
-      </c>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" s="27">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>분석02</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>링커코리아 주식회사</t>
-        </is>
-      </c>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" s="27">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>분석03</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>현대오토에버 주식회사</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="27">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>분석04</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>상품매출액(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" s="27">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>분석05</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>both</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" s="27">
-      <c r="A8" s="16" t="n"/>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" s="27">
-      <c r="A9" s="16" t="n"/>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="27">
-      <c r="A10" s="16" t="n"/>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" s="27">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="27">
-      <c r="A12" s="16" t="n"/>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>이자비용</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>단기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>유동성장기부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>유동성장기차입금</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>유동성리스부채</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>외화예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>당좌예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>정기성예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>정기예금</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>보험료(보증보험)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>보험료(세중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>보험료(세중S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>보험료(자동차보험)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>보험료-기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>판매비와관비지급수수료</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2003,18 +2426,18 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25" customWidth="1" style="27" min="1" max="1"/>
-    <col width="10" customWidth="1" style="27" min="2" max="3"/>
+    <col width="25" customWidth="1" style="28" min="1" max="1"/>
+    <col width="10" customWidth="1" style="28" min="2" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="27">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="28">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>구분: 차변(비용/손실), 대변(수익/이익), both(양쪽 합계) | 실행여부 Y인 행만 처리 | 거래처별 비교는 2번 메뉴 사용</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1" s="27">
+    <row r="2" ht="20" customHeight="1" s="28">
       <c r="A2" s="18" t="inlineStr">
         <is>
           <t>계정과목</t>
@@ -2036,7 +2459,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="27">
+    <row r="3" ht="18" customHeight="1" s="28">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>상품매출액(PLM)</t>
@@ -2058,7 +2481,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="27">
+    <row r="4" ht="18" customHeight="1" s="28">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>상품매출액(PLM)</t>
@@ -2080,7 +2503,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1" s="27">
+    <row r="5" ht="18" customHeight="1" s="28">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>상품매출액(PLM)</t>
@@ -2102,7 +2525,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" s="27">
+    <row r="6" ht="18" customHeight="1" s="28">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>상품매출액(S&amp;C)</t>
@@ -2124,32 +2547,32 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" s="27">
+    <row r="7" ht="18" customHeight="1" s="28">
       <c r="A7" s="19" t="n"/>
       <c r="B7" s="20" t="n"/>
       <c r="C7" s="20" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="27">
+    <row r="8" ht="18" customHeight="1" s="28">
       <c r="A8" s="19" t="n"/>
       <c r="B8" s="20" t="n"/>
       <c r="C8" s="20" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="27">
+    <row r="9" ht="18" customHeight="1" s="28">
       <c r="A9" s="19" t="n"/>
       <c r="B9" s="20" t="n"/>
       <c r="C9" s="20" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="27">
+    <row r="10" ht="18" customHeight="1" s="28">
       <c r="A10" s="19" t="n"/>
       <c r="B10" s="20" t="n"/>
       <c r="C10" s="20" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="27">
+    <row r="11" ht="18" customHeight="1" s="28">
       <c r="A11" s="19" t="n"/>
       <c r="B11" s="20" t="n"/>
       <c r="C11" s="20" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="27">
+    <row r="12" ht="18" customHeight="1" s="28">
       <c r="A12" s="19" t="n"/>
       <c r="B12" s="20" t="n"/>
       <c r="C12" s="20" t="n"/>
@@ -2168,14 +2591,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="36.75" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
-    <col width="10" customWidth="1" style="27" min="2" max="2"/>
-    <col width="12" customWidth="1" style="27" min="3" max="3"/>
-    <col width="10" customWidth="1" style="27" min="4" max="4"/>
-    <col width="55" customWidth="1" style="27" min="5" max="5"/>
+    <col width="27.33203125" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2186,137 +2605,96 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>외화환산손익</t>
+          <t>외상매출금(상품)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>당기손익-공정가치측정금융자산평가손익</t>
+          <t>미수금(기타)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대손상각비</t>
+          <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>파생상품평가손익</t>
+          <t>매출액(국제항공권취급수수료)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>매출액상품</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>매출액용역</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2326,47 +2704,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="22" customWidth="1" style="27" min="1" max="1"/>
-    <col width="26" customWidth="1" style="27" min="2" max="2"/>
-    <col width="10" customWidth="1" style="27" min="3" max="3"/>
-    <col width="55" customWidth="1" style="27" min="4" max="4"/>
+    <col width="36.75" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
+    <col width="10" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="10" customWidth="1" style="28" min="4" max="4"/>
+    <col width="55" customWidth="1" style="28" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>유형자산계정명</t>
+          <t>계정과목</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>감가상각누계액계정명</t>
+          <t>금액열</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>대체상대계정</t>
+          <t>그룹기준열</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>취득원가_수동조정</t>
+          <t>실행여부</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>상각누계액_수동조정</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2375,171 +2744,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>토지</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>토지는 감가상각 대상 아님(감가상각누계액 계정 없음). 취득원가 계정명도 당기/전기 이동 없어 분개장에 미노출 — 사용자 확인 예정 (2026-08-12)</t>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>건물</t>
+          <t>외화환산손익</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>건물감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>건물(투자)</t>
+          <t>당기손익-공정가치측정금융자산평가손익</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>건물(투자)감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>구축물</t>
+          <t>대손상각비</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>구축물감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>기계장치</t>
+          <t>파생상품평가손익</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>기계장치감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>기구비품</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>기구비품감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>차량운반구</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>차량감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료 (기존 예시의 차량운반구감가상각누계액 -&gt; 차량감가상각누계액으로 정정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>사용권자산</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>사용권자산감가상각누계액</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료 (신규 추가)</t>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>계정명/차대변 방향은 회사 실제 계정과목명에 맞게 조정 필요 (익/손 분리 계정이면 행 추가)</t>
         </is>
       </c>
     </row>
@@ -2554,26 +2862,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="22" customWidth="1" style="28" min="1" max="1"/>
+    <col width="26" customWidth="1" style="28" min="2" max="2"/>
+    <col width="10" customWidth="1" style="28" min="3" max="3"/>
+    <col width="55" customWidth="1" style="28" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>처분이익계정명</t>
+          <t>유형자산계정명</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>처분손실계정명</t>
+          <t>감가상각누계액계정명</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>대체상대계정</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>취득원가_수동조정</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상각누계액_수동조정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -2582,22 +2911,171 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>영업외수익(유형자산처분이익)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>영업외비용(유형자산처분손실)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>토지</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>토지는 감가상각 대상 아님(감가상각누계액 계정 없음). 취득원가 계정명도 당기/전기 이동 없어 분개장에 미노출 — 사용자 확인 예정 (2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>건물</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>건물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>실제 sejoong 계정과목명 확인됨 (2026-08-12). 단 감가상각_유형자산롤포워드 시트 계정명이 아직 예시 상태라 그것부터 확정 후 Y로 전환할 것</t>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>건물(투자)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>건물(투자)감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>구축물</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>구축물감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>계정명 확인 완료(사용자 확인: 건물/건물(투자)/구축물 그대로 사용 — 2026-08-12). 단 당기 중 취득·처분 거래가 없어 분개장에 노출되지 않고, 이 상태로 켜면 _account_match_flexible() 접두어 오매칭 버그가 재발하므로 그 수정 전까지 실행여부 N 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>기계장치</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>기계장치감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>기구비품</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>기구비품감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>차량운반구</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>차량감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료 (기존 예시의 차량운반구감가상각누계액 -&gt; 차량감가상각누계액으로 정정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>사용권자산</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>사용권자산감가상각누계액</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-12 sejoong 실제 분개장 계정명 확인 완료 (신규 추가)</t>
         </is>
       </c>
     </row>
@@ -2615,14 +3093,14 @@
   <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="12" customWidth="1" style="27" min="1" max="1"/>
-    <col width="27.83203125" customWidth="1" style="27" min="2" max="2"/>
-    <col width="72.5" bestFit="1" customWidth="1" style="27" min="3" max="3"/>
-    <col width="12" customWidth="1" style="27" min="4" max="4"/>
-    <col width="8" bestFit="1" customWidth="1" style="27" min="6" max="6"/>
+    <col width="12" customWidth="1" style="28" min="1" max="1"/>
+    <col width="27.83203125" customWidth="1" style="28" min="2" max="2"/>
+    <col width="106.83203125" bestFit="1" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="8" bestFit="1" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="27">
+    <row r="1" ht="18" customHeight="1" s="28">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>분석번호</t>
@@ -2654,7 +3132,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="27">
+    <row r="2" ht="16" customHeight="1" s="28">
       <c r="A2" s="6" t="n">
         <v>2</v>
       </c>
@@ -2670,7 +3148,7 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2682,7 +3160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="27">
+    <row r="3" ht="16" customHeight="1" s="28">
       <c r="A3" s="7" t="n">
         <v>3</v>
       </c>
@@ -2698,7 +3176,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2707,7 +3185,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="27">
+    <row r="4" ht="16" customHeight="1" s="28">
       <c r="A4" s="6" t="n">
         <v>4</v>
       </c>
@@ -2723,7 +3201,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2732,7 +3210,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="27">
+    <row r="5" ht="16" customHeight="1" s="28">
       <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
@@ -2748,7 +3226,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2757,7 +3235,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="27">
+    <row r="6" ht="16" customHeight="1" s="28">
       <c r="A6" s="6" t="n">
         <v>6</v>
       </c>
@@ -2782,7 +3260,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="27">
+    <row r="7" ht="16" customHeight="1" s="28">
       <c r="A7" s="7" t="n">
         <v>7</v>
       </c>
@@ -2823,7 +3301,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2873,7 +3351,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2898,7 +3376,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2923,7 +3401,7 @@
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2948,7 +3426,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2973,7 +3451,7 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3023,7 +3501,7 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3048,7 +3526,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3098,7 +3576,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3123,7 +3601,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3173,7 +3651,7 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3218,7 +3696,7 @@
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3243,7 +3721,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3281,7 +3759,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n">
+      <c r="A27" s="26" t="n">
         <v>27</v>
       </c>
       <c r="B27" s="25" t="inlineStr">
@@ -3294,9 +3772,9 @@
           <t>감가상각비 등 손익계정의 상대계정(자산 누계액 등) 금액을 8번과 동일 로직으로 추출 (Phase 1)</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="E27" s="25" t="inlineStr">
@@ -3331,6 +3809,64 @@
       <c r="C33" t="inlineStr">
         <is>
           <t>4,5,6,16,19,22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>처분이익계정명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>처분손실계정명</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>영업외수익(유형자산처분이익)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>영업외비용(유형자산처분손실)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>실제 sejoong 계정과목명 확인됨 (2026-08-12). 단 감가상각_유형자산롤포워드 시트 계정명이 아직 예시 상태라 그것부터 확정 후 Y로 전환할 것</t>
         </is>
       </c>
     </row>
@@ -3345,28 +3881,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="27.33203125" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="28">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>실행여부</t>
+        </is>
+      </c>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>매출액(국내호텔콘도알선수입)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>매출액(국제항공권판매수입)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>매출액(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>매출액(해외여행알선수입)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>상품매출액(정보기술)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>용역매출액(PLM)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>용역매출액(정보기술)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3383,35 +4090,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
+  <cols>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
+    <col width="10" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="42" customWidth="1" style="28" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="28">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>미수대매금(국제항공권판매)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="28">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>외상매출금(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="28">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>미수금(해외여행알선)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>미수금(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1" s="28">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>보통예금</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1" s="28">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>예수금(국제항공권환불)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>선급금(입체금-국내관광알선)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>선수금(국제항공권)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>매출액(국제항공취급수수료)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3421,29 +4307,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="27.33203125" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="27">
-      <c r="A1" s="22" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>금액열</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>그룹기준열</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>실행여부</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3452,15 +4343,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>매출액(국내호텔콘도알선수입)</t>
+          <t>보통예금</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>대변</t>
+          <t>차변</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3469,15 +4365,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>매출액(국제항공권판매수입)</t>
+          <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>대변</t>
+          <t>차변</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3486,15 +4387,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>매출액(국제항공취급수수료)</t>
+          <t>항공권판매(국제)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>대변</t>
+          <t>차변</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3503,15 +4409,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>매출액(해외여행알선수입)</t>
+          <t>외상매출금(PLM)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대변</t>
+          <t>차변</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3520,15 +4431,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>상품매출액(PLM)</t>
+          <t>미수금(해외여행알선)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>대변</t>
+          <t>차변</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3537,15 +4453,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>상품매출액(S&amp;C)</t>
+          <t>미수금(기 타)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>대변</t>
+          <t>차변</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3554,7 +4475,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>상품매출액(정보기술)</t>
+          <t>상품매출액(PLM)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3563,6 +4484,11 @@
         </is>
       </c>
       <c r="C8" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3571,7 +4497,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>용역매출액(PLM)</t>
+          <t>용역매출액(S&amp;C)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3580,6 +4506,11 @@
         </is>
       </c>
       <c r="C9" t="inlineStr">
+        <is>
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3588,7 +4519,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>용역매출액(S&amp;C)</t>
+          <t>미지급금(일반)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3598,22 +4529,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>용역매출액(정보기술)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+          <t>전표번호</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3630,91 +4549,108 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
+    <col width="16" customWidth="1" style="28" min="1" max="1"/>
+    <col width="10" customWidth="1" style="28" min="2" max="2"/>
+    <col width="16.6640625" customWidth="1" style="28" min="3" max="3"/>
+    <col width="12" customWidth="1" style="28" min="4" max="4"/>
+    <col width="36" customWidth="1" style="28" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1" s="28">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>항공권판매(국제)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>외상매출금(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>미수금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>미수금(기 타)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>외상매입금(상품)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>용역매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>용역매출액(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>미지급금(일반)</t>
-        </is>
-      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>금액열</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>최소금액</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>실행여부</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1" s="28">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" s="28">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>(전체)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>대변</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" s="28">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>보통예금</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>차변</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3724,650 +4660,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="26.1640625" bestFit="1" customWidth="1" style="27" min="2" max="2"/>
+    <col width="23.4140625" bestFit="1" customWidth="1" style="28" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>구분</t>
+          <t>거래처명</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>계정과목</t>
+          <t>실행여부</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>보통예금</t>
+          <t>(주)세중샤론손해보험중개</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매)</t>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>미수금환불(국제항공)</t>
+          <t>세중엔지니어링</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>정기예금</t>
+          <t>(주)세중엔지니어링</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>수탁금(해외여행알선)</t>
+          <t>(재)우리옛돌문화재단</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>외상매출금(S&amp;C)</t>
+          <t>㈜세중인터내셔널</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>투자매도가능증권</t>
+          <t>(주)세성항운</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>미수금(카드판매)</t>
+          <t>(주)세중로지스틱스</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>선급금(입체금-해외여행알선)</t>
+          <t>세중인터내셔널</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>상품(PLM)</t>
+          <t>천신일</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>미수금(호텔콘도판매)</t>
+          <t>천세전</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>미수금(국제항공취급수수료)</t>
+          <t>천호전</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>상품(S&amp;C)</t>
+          <t>천미전</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>수탁금(호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>선급금(입체금-호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>선급금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>정기성예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>선급금(일반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>장기대여금</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>미수금(국제항공권-정산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>미수수익</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>자산</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>외화예금</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>가수금</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>항공권판매(국제)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>예수금(국제항공권환불)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>미지급금(국제항공권-정산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>미지급금(일반)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>선수금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>외상매입금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>미지급금(해외여행알선)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>외상매입금(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>미지급금(호텔콘도판매)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>미지급금(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>예수금(결산)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>미지급금(회사카드사용분-단체)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>부채</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>예수금(갑근세)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>용역매출액(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>상품매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>항공권판매(국제항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>매출액(국제항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>상품매출액(S&amp;C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>매출액(기타항공권판매수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>매출액(해외여행알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>매출액(해외호텔알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>용역매출액(PLM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>매출액(국내관광알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>매출액(국제항공권판매수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>매출액(여권비자취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>매출액(국내호텔콘도알선수입)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>매출액(기타)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>매출액(국내항공취급수수료)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>매출액(국내항공권판매수입)</t>
-        </is>
-      </c>
+      <c r="B15" s="8" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4377,234 +4848,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
-  <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>계정과목</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>그룹기준열</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>보통예금</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매출금(상품)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>미수대매금(국제항공권판매)</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미수금(해외여행알선)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>항공권판매(국제)</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미수금(기타)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>외상매출금(PLM)</t>
+          <t>자산</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미수대매금(국제항공권판매)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>미수금(해외여행알선)</t>
+          <t>부채</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>외상매입금(상품)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>미수금(기 타)</t>
+          <t>부채</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미지급금(일반)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>상품매출액(PLM)</t>
+          <t>부채</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>미지급금(기타)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>용역매출액(S&amp;C)</t>
+          <t>부채</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>미지급금(일반)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>전표번호</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>선수금(해외여행알선)</t>
         </is>
       </c>
     </row>
@@ -4619,213 +4970,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
-    <col width="25.4140625" bestFit="1" customWidth="1" style="27" min="1" max="1"/>
-    <col width="10" customWidth="1" style="27" min="2" max="2"/>
-    <col width="12" customWidth="1" style="27" min="3" max="3"/>
-    <col width="42" customWidth="1" style="27" min="4" max="4"/>
+    <col width="25.4140625" bestFit="1" customWidth="1" style="28" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="27">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>계정과목</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>금액열</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>실행여부</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="27">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>미수대매금(국제항공권판매)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="27">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>외상매출금(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="27">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>미수금(해외여행알선)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>용역매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>상품매출액(PLM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>매출액(국제항공취급수수료)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>미수금(국제항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="27">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>보통예금</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>차변</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="27">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>예수금(국제항공권환불)</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n"/>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>상품매출액(S&amp;C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>매출액(기타항공권판매수입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>지급수수료(S&amp;C)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>선급금(입체금-국내관광알선)</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>지급수수료(PLM)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>선수금(국제항공권)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>용역매출액(S&amp;C)</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>매출액(국제항공취급수수료)</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>대변</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>비용</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>접대비</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>